--- a/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -555,17 +555,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -576,16 +576,16 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Les ratios au 31 octobre 2025 tiennent compte du rachat des billets de capital à recours limité série 1 (BCRL - Série 1) effectué le 17 novembre 2025.</t>
+          <t>Ratio de liquidité à court terme</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Capital réglementaire
-Ce qui change : L'indicateur 'Prêts et acceptations, déduction faite des provisions' a été remplacé par 'Prêts, déduction faite des provisions'. De plus, une note a été ajoutée concernant le rachat des billets de capital à recours limité série 1.
-Pertinence métier : Ce changement met l'accent sur la manière dont la banque ajuste ses indicateurs de capital, ce qui peut avoir un impact sur la perception de sa solidité financière. Le rachat des billets de capital à recours limité série 1 est particulièrement pertinent pour les exigences de capital réglementaire, car il peut affecter la composition des fonds propres réglementaires.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les ratios de capital réglementaire et la manière dont ils sont perçus par les régulateurs et les investisseurs.</t>
+Sujet détecté : Liquidité et structure du rapport
+Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées.
+Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption.
+Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -594,28 +594,36 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:01:44.298197+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -630,21 +638,21 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Certains montants ont été ajustés à la suite de modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
+          <t>Inclut les billets de dépôt au porteur.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Le 3 février 2025, la Banque a conclu l’acquisition de CWB. Les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a eu une incidence sur les résultats, les soldes et les ratios pour l’exercice terminé le 31 octobre 2025. Consulter la section « Acquisition » pour de plus amples renseignements sur l’incidence de l’acquisition de CWB.</t>
+          <t>Incluent les dettes qui font l’objet de règlements sur la conversion aux fins de la recapitalisation interne des banques.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Capital réglementaire
-Ce qui change : L'indicateur 'Prêts et acceptations, déduction faite des provisions' a été remplacé par 'Prêts, déduction faite des provisions'. De plus, une note a été ajoutée concernant le rachat des billets de capital à recours limité série 1.
-Pertinence métier : Ce changement met l'accent sur la manière dont la banque ajuste ses indicateurs de capital, ce qui peut avoir un impact sur la perception de sa solidité financière. Le rachat des billets de capital à recours limité série 1 est particulièrement pertinent pour les exigences de capital réglementaire, car il peut affecter la composition des fonds propres réglementaires.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les ratios de capital réglementaire et la manière dont ils sont perçus par les régulateurs et les investisseurs.</t>
+Sujet détecté : Structure du rapport, Texte de risque modifié
+Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
+Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
+Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -659,22 +667,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -684,26 +692,22 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>À la lumière de la loi adoptée concernant les dividendes canadiens, la Banque n’a pas comptabilisé de déduction d’impôts sur le résultat ni utilisé la méthode de l’équivalent imposable pour ajuster les revenus liés aux dividendes visés, reçus après le 1er janvier 2024 (pour de plus amples renseignements, se reporter à la section « Impôts sur le résultat »).</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Le 3 février 2025, la Banque a conclu l’acquisition de CWB. Les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a eu une incidence sur les résultats, les soldes et les ratios pour l’exercice terminé le 31 octobre 2025. Consulter la section « Acquisition » pour de plus amples renseignements sur l’incidence de l’acquisition de CWB.</t>
-        </is>
-      </c>
+          <t>Inclut les dettes qui font l’objet de règlements sur la conversion aux fins de la recapitalisation interne des banques.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
 Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
+Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
+Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -716,68 +720,68 @@
       <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Modification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Certains montants ont été ajustés à la suite de modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Le 3 février 2025, la Banque a conclu l’acquisition de CWB. Les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a eu une incidence sur les résultats, les soldes et les ratios pour l’exercice terminé le 31 octobre 2025. Consulter la section « Acquisition » pour de plus amples renseignements sur l’incidence de l’acquisition de CWB.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Une révision en profondeur incluant des données plus récentes est en cours de validation et sera déployée dans les prochains trimestres.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Une révision en profondeur incluant des données plus récentes a récemment été approuvée par le groupe de validation des modèles et sera déployée dans la prochaine année. Il convient de préciser que, pour le calcul du capital réglementaire, des estimations de PCD prescrites par le BSIF sont utilisées pour toutes les facilités d’institutions financières.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non
+Sujet détecté : Reformulation sans nouveau fond
+Ce qui change : La note a été modifiée de 'Une révision en profondeur incluant des données plus récentes est en cours de va' à 'Une révision en profondeur incluant des données plus récentes a récemment été ap'.
+Pertinence métier : Ce changement est une simple reformulation de la note sans ajout de contenu substantiel ou de nouvelle information réglementaire. Il n'affecte pas la substance de la divulgation ni ne modifie la posture de la banque en matière de gestion des risques.
+Point de surveillance : Aucun point de surveillance requis car il s'agit d'une reformulation sans impact sur les attentes réglementaires ou la gestion des risques.</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,37 +791,41 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Certains montants ont été ajustés à la suite de modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
+        </is>
+      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Positions liées aux activités de négociation pour lesquelles la mesure de risque est la VaR totale. Pour de plus amples renseignements, se reporter au tableau illustrant la distribution de la VaR des portefeuilles de négociation par catégorie de risque et leur effet de diversification présenté à la page suivante.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
 Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
-Ce qui change : L'indicateur 'Acquisition' a été ajouté, 'Modifications de méthodes comptables' a été supprimé, et 'Marchés financiers' a été renommé en 'Marchés des capitaux'.
-Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de gestion du capital, ce qui peut refléter une évolution dans la manière dont la banque gère ses acquisitions et ses interactions avec les marchés des capitaux. La suppression de l'indicateur lié aux méthodes comptables pourrait indiquer une stabilisation ou une standardisation des pratiques comptables.
-Point de surveillance : Surveiller comment ces changements d'indicateurs affectent la gestion du capital et les rapports financiers de la banque, notamment en ce qui concerne les acquisitions et les marchés des capitaux.</t>
+Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
+Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
+Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -832,7 +840,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -842,12 +850,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -857,10 +865,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
+          <t>Renommage</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Prêts et acceptations, déduction faite des provisions</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Prêts, déduction faite des provisions</t>
@@ -869,10 +881,10 @@
       <c r="I7" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Capital réglementaire
-Ce qui change : L'indicateur 'Prêts et acceptations, déduction faite des provisions' a été remplacé par 'Prêts, déduction faite des provisions'. De plus, une note a été ajoutée concernant le rachat des billets de capital à recours limité série 1.
-Pertinence métier : Ce changement met l'accent sur la manière dont la banque ajuste ses indicateurs de capital, ce qui peut avoir un impact sur la perception de sa solidité financière. Le rachat des billets de capital à recours limité série 1 est particulièrement pertinent pour les exigences de capital réglementaire, car il peut affecter la composition des fonds propres réglementaires.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les ratios de capital réglementaire et la manière dont ils sont perçus par les régulateurs et les investisseurs.</t>
+Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
+Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
+Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
+Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -887,7 +899,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,37 +909,37 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Certains montants ont été ajustés à la suite de la cessation de la présentation des revenus et de la charge d’impôts selon la méthode de l’équivalent imposable.</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Acceptations</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Capital réglementaire
-Ce qui change : L'indicateur 'Prêts et acceptations, déduction faite des provisions' a été remplacé par 'Prêts, déduction faite des provisions'. De plus, une note a été ajoutée concernant le rachat des billets de capital à recours limité série 1.
-Pertinence métier : Ce changement met l'accent sur la manière dont la banque ajuste ses indicateurs de capital, ce qui peut avoir un impact sur la perception de sa solidité financière. Le rachat des billets de capital à recours limité série 1 est particulièrement pertinent pour les exigences de capital réglementaire, car il peut affecter la composition des fonds propres réglementaires.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les ratios de capital réglementaire et la manière dont ils sont perçus par les régulateurs et les investisseurs.</t>
+Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
+Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
+Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
+Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -942,7 +954,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -952,17 +964,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -972,7 +984,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Modifications de méthodes comptables</t>
+          <t>Positions liées aux activités de négociation pour lesquelles la mesure du risque est la VaR totale. Pour de plus amples renseignements, se reporter au tableau illustrant la distribution de la VaR des portefeuilles de négociation par catégorie de risque et leur effet de diversification présenté à la page suivante.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
@@ -980,9 +992,9 @@
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
 Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
-Ce qui change : L'indicateur 'Acquisition' a été ajouté, 'Modifications de méthodes comptables' a été supprimé, et 'Marchés financiers' a été renommé en 'Marchés des capitaux'.
-Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de gestion du capital, ce qui peut refléter une évolution dans la manière dont la banque gère ses acquisitions et ses interactions avec les marchés des capitaux. La suppression de l'indicateur lié aux méthodes comptables pourrait indiquer une stabilisation ou une standardisation des pratiques comptables.
-Point de surveillance : Surveiller comment ces changements d'indicateurs affectent la gestion du capital et les rapports financiers de la banque, notamment en ce qui concerne les acquisitions et les marchés des capitaux.</t>
+Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
+Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
+Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -997,7 +1009,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1007,12 +1019,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1027,17 +1039,17 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Prêts et acceptations, déduction faite des provisions</t>
+          <t>Participations dans des entreprises associées et des coentreprises</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Capital réglementaire
-Ce qui change : L'indicateur 'Prêts et acceptations, déduction faite des provisions' a été remplacé par 'Prêts, déduction faite des provisions'. De plus, une note a été ajoutée concernant le rachat des billets de capital à recours limité série 1.
-Pertinence métier : Ce changement met l'accent sur la manière dont la banque ajuste ses indicateurs de capital, ce qui peut avoir un impact sur la perception de sa solidité financière. Le rachat des billets de capital à recours limité série 1 est particulièrement pertinent pour les exigences de capital réglementaire, car il peut affecter la composition des fonds propres réglementaires.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les ratios de capital réglementaire et la manière dont ils sont perçus par les régulateurs et les investisseurs.</t>
+Sujet détecté : Liquidité et structure du rapport
+Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées.
+Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption.
+Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1046,53 +1058,61 @@
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24T22:01:45.441911+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>(sans titre)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Prêts dépréciés bruts</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Certains montants ont été ajustés à la suite de modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Sujet détecté : Liquidité et structure du rapport
+Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées.
+Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption.
+Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1107,52 +1127,56 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Exigences de déclaration relatives au ratio de liquidité à long terme (1) (2) *</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Les valeurs pondérées sont calculées après l’application des pondérations prescrites par la ligne directrice NI du BSIF.</t>
+        </is>
+      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Prêts dépréciés nets</t>
+          <t>Les valeurs pondérées sont calculées après l’application des pondérations prescrites par la ligne directrice NL du BSIF.</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+          <t>NON — Nouvel élément à surveiller : Non
+Sujet détecté : Aucune modification substantielle
+Ce qui change : La note de bas de tableau a été reformulée sans changement de fond, avec une phrase identique à celle du rapport précédent.
+Pertinence métier : Ce changement n'apporte aucune nouvelle information ou modification substantielle à la divulgation existante. Il s'agit d'une reformulation sans impact sur la compréhension ou la gestion des risques de liquidité.
+Point de surveillance : Aucun point de surveillance requis, car il n'y a pas de changement substantiel à analyser.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
@@ -1162,22 +1186,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Notations de crédit de la Banque</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1193,16 +1217,16 @@
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
+          <t>Le 17 octobre 2025, S&amp;P Global Ratings (S&amp;P) a révisé à la hausse la notation de la dette à long terme de premier rang non assujettie au régime de recapitalisation interne des banques, la dette à long terme de premier rang, la dette subordonnée FPUNV, les billets de capital à recours limité FPUNV et les actions privilégiées FPUNV de la Banque.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Sujet détecté : Texte de risque modifié
+Ce qui change : La note de S&amp;P Global Ratings a été révisée à la hausse pour la dette à long terme de premier rang, tandis que la mention de Moody's concernant la révision à la hausse a été supprimée.
+Pertinence métier : Ce changement met en évidence une modification dans la perception du risque de crédit de la banque par les agences de notation. Une révision à la hausse par S&amp;P peut indiquer une amélioration de la situation financière ou de la gestion des risques de la banque, ce qui est crucial pour les investisseurs et les régulateurs. La suppression de la mention de Moody's pourrait également signaler un changement dans l'évaluation des risques ou des attentes du marché.
+Point de surveillance : Surveiller l'impact de ces changements de notation sur la perception du risque de crédit de la banque et ses implications pour le coût du financement et la conformité réglementaire.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1217,22 +1241,22 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Notations de crédit de la Banque</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1242,26 +1266,22 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Certains montants ont été ajustés à la suite de modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Consulter le « Mode de présentation de l’information » aux pages 18 à 23 pour de plus amples renseignements sur les mesures de gestion du capital.</t>
-        </is>
-      </c>
+          <t>Le 24 septembre 2024, Moody's a placé sous révision en vue d’une révision à la hausse toutes les notations et évaluations à long terme de la Banque, y compris son évaluation de crédit de base Baa1, les notations de dépôts à long terme Aa3 et les notations de risque de contrepartie, ainsi que son évaluation de risque de contrepartie de Aa3(cr).</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Sujet détecté : Texte de risque modifié
+Ce qui change : La note de S&amp;P Global Ratings a été révisée à la hausse pour la dette à long terme de premier rang, tandis que la mention de Moody's concernant la révision à la hausse a été supprimée.
+Pertinence métier : Ce changement met en évidence une modification dans la perception du risque de crédit de la banque par les agences de notation. Une révision à la hausse par S&amp;P peut indiquer une amélioration de la situation financière ou de la gestion des risques de la banque, ce qui est crucial pour les investisseurs et les régulateurs. La suppression de la mention de Moody's pourrait également signaler un changement dans l'évaluation des risques ou des attentes du marché.
+Point de surveillance : Surveiller l'impact de ces changements de notation sur la perception du risque de crédit de la banque et ses implications pour le coût du financement et la conformité réglementaire.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1276,22 +1296,22 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Sommaire des actifs grevés et non grevés (1) *</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1306,17 +1326,17 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Résultats d'exploitation</t>
+          <t>Participations dans des entreprises associées et des coentreprises</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Sujet détecté : Information retirée
+Ce qui change : L'indicateur 'Participations dans des entreprises associées et des coentreprises' a été supprimé du tableau 'Sommaire des actifs grevés et non grevés'.
+Pertinence métier : Ce changement met en évidence une modification dans la structure de la divulgation des actifs grevés et non grevés. La suppression de cet indicateur peut affecter la transparence et la comparabilité des informations sur les actifs de la banque, ce qui est crucial pour les investisseurs et les régulateurs qui surveillent l'exposition et la gestion des actifs.
+Point de surveillance : Surveiller l'impact de cette suppression sur la compréhension des actifs grevés et non grevés, et évaluer si cela affecte la conformité aux attentes de divulgation réglementaire.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1331,22 +1351,22 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1361,7 +1381,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Revenu net d’intérêts</t>
+          <t>Titrisation de créances sur cartes de crédit</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
@@ -1369,9 +1389,9 @@
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
 Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
+Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
+Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1386,27 +1406,27 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1416,7 +1436,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Revenus autres que d'intérêts</t>
+          <t>Les certificats de dépôt libellés en euros sont inclus dans les billets de premier rang non garantis à moyen terme.</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
@@ -1424,9 +1444,9 @@
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
 Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
+Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
+Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1446,17 +1466,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1466,22 +1486,22 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Revenu total</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Série 47</t>
+        </is>
+      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Sujet détecté : Capital réglementaire
+Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres.
+Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement.
+Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1501,17 +1521,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1521,22 +1541,22 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Frais autres que d'intérêts</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Série 49</t>
+        </is>
+      </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Sujet détecté : Capital réglementaire
+Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres.
+Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement.
+Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1556,17 +1576,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1581,17 +1601,17 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Résultat avant dotations aux pertes de crédit et charge d'impôts</t>
+          <t>Série 32</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Sujet détecté : Capital réglementaire
+Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres.
+Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement.
+Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1611,42 +1631,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Capital réglementaire (1), ratio de levier (1) et TLAC (2)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Résultat avant charge (économie) d'impôts</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Sujet détecté : Capital réglementaire
+Ce qui change : Une note a été ajoutée indiquant que les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.
+Pertinence métier : Ce changement met l'accent sur l'impact des opérations de rachat sur le capital réglementaire de la banque. Le rachat des BCRL - Série 1 peut affecter la composition des fonds propres réglementaires, ce qui est crucial pour la conformité aux exigences de capital. Cela souligne l'importance de surveiller les ajustements dans la structure du capital qui peuvent influencer les ratios prudentiels et la capacité de la banque à répondre aux attentes réglementaires.
+Point de surveillance : Surveiller l'impact du rachat des BCRL - Série 1 sur les ratios de capital et la conformité aux exigences réglementaires, en particulier en ce qui concerne le TLAC et le ratio de levier.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1666,42 +1686,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Charge (économie) d'impôts</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
+        </is>
+      </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Sujet détecté : Exigences réglementaires ou conformité, Ratio ou seuil prudentiel
+Ce qui change : La note modifiée indique un changement de date concernant la confirmation par le BSIF de la réserve pour stabilité intérieure, passant du 18 juin 2024 au 26 juin 2025. De plus, une nouvelle note mentionne que les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.
+Pertinence métier : Ce changement met en évidence une mise à jour des exigences réglementaires et des ratios prudentiels, ce qui est crucial pour la conformité et la gestion des fonds propres de la banque. La modification de la date de confirmation par le BSIF peut indiquer un ajustement dans les attentes réglementaires, tandis que la prise en compte du rachat des BCRL dans les ratios souligne l'impact des décisions de financement sur les exigences de capital.
+Point de surveillance : Surveiller l'impact de ces changements sur les ratios de fonds propres et la conformité aux exigences du BSIF, ainsi que l'effet du rachat des BCRL sur la structure de capital.</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1721,42 +1741,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Profil de risque</t>
+          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Résultat net</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisée conformément à l’approche utilisée par la Banque.</t>
+        </is>
+      </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
+Sujet détecté : Méthode de calcul ou approche modifiée
+Ce qui change : Inclusion de CWB dans le calcul du risque opérationnel au cours du deuxième trimestre de 2025.
+Pertinence métier : Ce changement met l'accent sur une modification méthodologique dans le calcul du risque opérationnel, ce qui peut avoir un impact sur les exigences de capital réglementaire de la banque. L'inclusion de CWB pourrait modifier la pondération des actifs en fonction des risques, influençant ainsi les ratios de capital réglementaire. Cela est crucial pour la conformité aux attentes prudentielles et pour la comparabilité entre pairs.
+Point de surveillance : Surveiller l'impact de l'inclusion de CWB sur les ratios de capital et s'assurer que la banque reste conforme aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1776,17 +1796,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
+          <t>Variation des fonds propres réglementaires (1)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1802,16 +1822,16 @@
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Amortissement des immobilisations incorporelles liées à l'acquisition de CWB (6)</t>
+          <t>Émission d'actions ordinaires relatives à l'acquisition de CWB</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
+Sujet détecté : Fonds propres réglementaires, Structure du rapport
+Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025.
+Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres.
+Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1820,16 +1840,8 @@
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-14T06:14:04.504816+00:00</t>
-        </is>
-      </c>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1839,17 +1851,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
+          <t>Variation des fonds propres réglementaires (1)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1865,16 +1877,16 @@
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Dotations aux pertes de crédit initiales sur les prêts non dépréciés acquis de CWB (7)</t>
+          <t>Options de remplacement relatives à l'acquisition de CWB</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
+Sujet détecté : Fonds propres réglementaires, Structure du rapport
+Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025.
+Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres.
+Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1894,42 +1906,46 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
+          <t>Variation des fonds propres réglementaires (1)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Les données de 2023 n’ont pas été ajustées pour tenir compte des modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
+        </is>
+      </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Économie d'impôts liée à un changement de traitement fiscal (8)</t>
+          <t>Les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
+Sujet détecté : Fonds propres réglementaires, Structure du rapport
+Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025.
+Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres.
+Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1942,1013 +1958,627 @@
       <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter aux notes 17 et 18 afférentes aux états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
+Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
+Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
+Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter aux notes 18 et 19 afférentes aux états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter à la note 23 afférente aux états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
+Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
+Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
+Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter à la note 25 afférente aux états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
+Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
+Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
+Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Incluent les billets de dépôt au porteur.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Structure du rapport, Texte de risque modifié
+Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
+Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
+Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Les acceptations bancaires ne sont pas incluses dans ce tableau.</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Structure du rapport, Texte de risque modifié
+Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
+Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
+Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Le 18 juin 2024, le BSIF a confirmé que la réserve pour stabilité intérieure était maintenue à 3,5 %.</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Le 26 juin 2025, le BSIF a confirmé que la réserve pour stabilité intérieure était maintenue à 3,5%.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Exigences réglementaires ou conformité, Ratio ou seuil prudentiel
+Ce qui change : La note modifiée indique un changement de date concernant la confirmation par le BSIF de la réserve pour stabilité intérieure, passant du 18 juin 2024 au 26 juin 2025. De plus, une nouvelle note mentionne que les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.
+Pertinence métier : Ce changement met en évidence une mise à jour des exigences réglementaires et des ratios prudentiels, ce qui est crucial pour la conformité et la gestion des fonds propres de la banque. La modification de la date de confirmation par le BSIF peut indiquer un ajustement dans les attentes réglementaires, tandis que la prise en compte du rachat des BCRL dans les ratios souligne l'impact des décisions de financement sur les exigences de capital.
+Point de surveillance : Surveiller l'impact de ces changements sur les ratios de fonds propres et la conformité aux exigences du BSIF, ainsi que l'effet du rachat des BCRL sur la structure de capital.</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2025, des dotations aux pertes de crédit initiales de 230 M$ (166 M$ déduction faite des impôts) ont été enregistrées sur les prêts non dépréciés acquis de CWB.</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Information ajoutée, Gouvernance des risques
+Ce qui change : Un nouveau tableau a été ajouté dans la section gestion des risques, listant divers types de risques, y compris le risque de non-conformité à la réglementation et le risque environnemental et social.
+Pertinence métier : Ce changement met l'accent sur une approche plus holistique de la gestion des risques en incluant une gamme étendue de risques, tels que le risque environnemental et social, qui sont de plus en plus pertinents dans le contexte actuel de réglementation accrue et de préoccupations ESG. Cela reflète une volonté de la banque de renforcer sa gouvernance des risques en intégrant des facteurs de risque plus diversifiés.
+Point de surveillance : Surveiller comment cette nouvelle divulgation influence la stratégie de gestion des risques de la banque et si elle entraîne des ajustements dans les processus de gouvernance des risques.</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Information retirée, Risque émergent : cybersécurité
+Ce qui change : Le tableau concernant les indicateurs de sécurité de l'information a été supprimé dans le rapport courant.
+Pertinence métier : Ce changement met en évidence une potentielle réduction de la transparence sur la gestion des risques liés à la cybersécurité. La sécurité de l'information est un domaine critique, surtout avec l'augmentation des cyberattaques. La suppression de ce tableau pourrait indiquer un changement de posture ou une réévaluation de la manière dont ces informations sont communiquées aux parties prenantes.
+Point de surveillance : Il est crucial de surveiller si cette suppression est compensée par d'autres formes de divulgation ou si elle reflète un changement dans la gestion des risques de cybersécurité.</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2025, une économie d’impôts de 47 M$ a été enregistrée en lien avec un changement de traitement fiscal relatif aux gains non réalisés comptabilisés au cours de l’exercice 2024 et du premier trimestre de 2025 suite à la réévaluation à la juste valeur de la participation que la Banque détenait dans CWB avant l’acquisition.</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Information ajoutée
+Ce qui change : Un nouveau tableau a été ajouté dans la section gestion du capital, présentant des indicateurs pour le crédit, le marché, l'opérationnel, et d'autres risques, ainsi qu'un total.
+Pertinence métier : Ce changement met en évidence une nouvelle approche de la banque pour divulguer des informations sur la gestion du capital. L'ajout de ce tableau pourrait indiquer une volonté de transparence accrue ou une réponse à des attentes réglementaires spécifiques concernant la gestion des risques et du capital. Cela permet une meilleure comparabilité entre pairs et peut refléter une adaptation aux exigences prudentielles.
+Point de surveillance : Surveiller si ce tableau est lié à de nouvelles exigences réglementaires ou à une modification de la stratégie de gestion du capital de la banque.</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2024, un montant de 14 M$ (10 M$ déduction faite des impôts) a été enregistré, représentant l’amortissement des frais d'émission des reçus de souscription émis dans le cadre de l’entente visant l’acquisition de CWB (pour de plus amples renseignements, se reporter aux notes 14 et 16 afférentes aux présents états financiers consolidés).</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2025, un montant de 28 M$ (20 M$ déduction faite des impôts) a été enregistré, représentant l’amortissement des frais d'émission des reçus de souscription émis dans le cadre de l’entente visant l’acquisition de CWB (2024 : 14 M$, 10 M$ déduction faite des impôts). Pour de plus amples renseignements, se reporter aux notes 13 et 15 afférentes aux états financiers consolidés.</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Structure du rapport, Capital réglementaire
+Ce qui change : Un nouveau tableau a été ajouté dans la section capital_management, présentant des indicateurs pour le Crédit, le Marché, l'Opérationnel et le Total.
+Pertinence métier : Ce changement met l'accent sur la transparence accrue dans la gestion du capital de la banque. L'ajout de ce tableau permet une meilleure compréhension des composantes du capital réglementaire, ce qui est crucial pour la conformité aux exigences prudentielles et pour la comparabilité entre pairs.
+Point de surveillance : Surveiller l'impact de ce nouveau tableau sur la divulgation des ratios de capital et s'assurer qu'il est aligné avec les attentes réglementaires en matière de transparence et de gestion du capital.</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2024, un gain de 174 M$ (125 M$ déduction faite des impôts) a été enregistré, résultant de la réévaluation à la juste valeur de la participation que la Banque détient dans CWB.</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2025, un gain de 4 M$ a été enregistré, résultant de la réévaluation à la juste valeur de la participation que la Banque détenait dans CWB avant l’acquisition (2024 : 174 M$, 125 M$ déduction faite des impôts).</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Structure du rapport, Capital réglementaire
+Ce qui change : Un nouveau tableau a été ajouté dans la section gestion du capital, présentant des indicateurs pour le crédit, le marché, l'opérationnel et le total.
+Pertinence métier : Ce changement met en évidence une nouvelle approche de la banque pour divulguer des informations sur ses indicateurs de capital. Cela pourrait refléter une réponse aux attentes réglementaires accrues en matière de transparence et de gestion des risques. La présentation de ces indicateurs est cruciale pour évaluer la santé financière de la banque et sa conformité aux exigences de capital réglementaire.
+Point de surveillance : Surveiller comment ces indicateurs influencent la gestion du capital et la conformité réglementaire de la banque, ainsi que toute mise à jour future de la méthodologie de calcul ou de présentation.</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2023, la Banque avait conclu qu’elle avait perdu l’influence notable sur Groupe TMX limitée (TMX) et avait donc cessé la comptabilisation selon la méthode de la mise en équivalence de ce placement. La Banque avait désigné son placement dans TMX comme étant un actif financier évalué à la juste valeur par le biais des autres éléments du résultat global, à un montant de 191 M$. Lors de l’évaluation à la juste valeur, un gain de 91 M$ (67 M$ déduction faite des impôts) avait été enregistré.</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2025, la Banque a comptabilisé une perte de 23 M$ (17 M$ déduction faite des impôts) liée à la réévaluation à la juste valeur des swaps de taux d’intérêt utilisés pour la gestion des variations de la juste valeur des actifs et passifs de CWB qui donnaient lieu à la volatilité du goodwill et des fonds propres à la clôture de la transaction (2024 : 3 M$, 2 M$ déduction faite des impôts).</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2024, la Banque a comptabilisé une perte de 3 M$ (2 M$ déduction faite des impôts) liée à la réévaluation à la juste valeur des swaps de taux d’intérêt utilisés pour la gestion des variations de la juste valeur des actifs et passifs de CWB qui donnent lieu à la volatilité du goodwill et des fonds propres à la clôture de la transaction. Pour de plus amples renseignements, se reporter à la section « Transaction CWB ».</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2025, des charges d'acquisition et d'intégration de 352 M$ (255 M$ déduction faite des impôts) ont été enregistrées relativement à la transaction avec CWB (2024 : 18 M$, 13 M$ déduction faite des impôts).</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2024, des charges d'acquisition et d'intégration de 18 M$ (13 M$ déduction faite des impôts) ont été enregistrées relativement à la transaction CWB.</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2025, un montant de 73 M$ (54 M$ déduction faite des impôts) a été enregistré, représentant l’amortissement des immobilisations incorporelles liées à l’acquisition de CWB.</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Renommage</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Gain sur réévaluation à la juste valeur de participations (3) (4)</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Gain sur réévaluation à la juste valeur d'une participation (3)</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Pertes de valeur d'immobilisations corporelles et incorporelles (7)</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Charges pour litiges (8)</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Charge liée aux modifications à la Loi sur la taxe d'accise (9)</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Provisions pour contrats (10)</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Présentation du résultat de base et dilué par action – ajustés</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Charge d'impôts liée aux mesures fiscales 2022 du gouvernement du Canada (11)</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Information retirée, Texte de risque modifié
-Ce qui change : Des indicateurs ont été ajoutés et supprimés dans le tableau 'Présentation du résultat de base et dilué par action – ajustés', notamment l'ajout de l'amortissement des immobilisations incorporelles liées à l'acquisition de CWB et la suppression de charges pour litiges.
-Pertinence métier : Ce changement met l'accent sur la réévaluation des éléments comptables liés aux acquisitions et aux traitements fiscaux, ce qui peut avoir un impact sur la perception des résultats financiers ajustés de la banque. Les ajustements reflètent des changements dans la stratégie de gestion des acquisitions et des litiges, ce qui est crucial pour la transparence et la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ces ajustements sur les résultats financiers ajustés et la manière dont ils influencent la communication des performances financières de la banque.</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>(sans titre)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Renommage</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>Marchés financiers</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>Marchés des capitaux</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
-Ce qui change : L'indicateur 'Acquisition' a été ajouté, 'Modifications de méthodes comptables' a été supprimé, et 'Marchés financiers' a été renommé en 'Marchés des capitaux'.
-Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de gestion du capital, ce qui peut refléter une évolution dans la manière dont la banque gère ses acquisitions et ses interactions avec les marchés des capitaux. La suppression de l'indicateur lié aux méthodes comptables pourrait indiquer une stabilisation ou une standardisation des pratiques comptables.
-Point de surveillance : Surveiller comment ces changements d'indicateurs affectent la gestion du capital et les rapports financiers de la banque, notamment en ce qui concerne les acquisitions et les marchés des capitaux.</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="4" t="inlineStr"/>
-      <c r="M40" s="4" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Profil de risque</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Incluant les engagements de clients en contrepartie d’acceptations pour les exercices 2021 à 2024.</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="4" t="inlineStr"/>
-      <c r="M41" s="4" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Profil de risque</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>Au cours de l’exercice terminé le 31 octobre 2024, un montant de 14 M$ (10 M$ déduction faite des impôts) a été enregistré, représentant l’amortissement des frais d'émission des reçus de souscription émis dans le cadre de l'entente visant l’acquisition de CWB (pour de plus amples renseignements, se reporter aux notes 14 et 16 afférentes aux présents états financiers consolidés).</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>Consulter le « Glossaire » aux pages 136 à 139 pour plus de détails sur la composition de ces mesures.</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : Les indicateurs 'Prêts dépréciés bruts' et 'Prêts dépréciés nets' ont été ajoutés, tandis que plusieurs indicateurs financiers ont été supprimés du tableau 'Profil de risque'. De plus, des notes ont été ajoutées et modifiées, notamment concernant les engagements de clients et des acquisitions récentes.
-Pertinence métier : Ce changement met l'accent sur une réorientation de l'analyse du profil de risque vers les prêts dépréciés, ce qui peut indiquer une attention accrue sur la qualité des actifs et la gestion des risques de crédit. La suppression des indicateurs financiers traditionnels pourrait refléter un changement de priorité dans la communication des risques. Les nouvelles notes ajoutées fournissent un contexte supplémentaire sur les engagements et les événements récents, ce qui est crucial pour comprendre l'impact sur le profil de risque.
-Point de surveillance : Surveiller l'impact de ces changements sur la perception du risque de crédit et la manière dont la banque communique ses priorités en matière de gestion des risques.</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr"/>
-      <c r="M42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Tableau</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information retirée, Risque climatique / ESG
-Ce qui change : Le tableau concernant les initiatives ESG, incluant la lutte contre les changements climatiques, la transition énergétique, et l'inclusion sociale, a été supprimé du rapport T2.
-Pertinence métier : Ce changement met en évidence un retrait d'informations cruciales sur les engagements ESG de la banque, ce qui pourrait affecter la transparence et la perception de la banque en matière de responsabilité environnementale et sociale. Les investisseurs et régulateurs s'attendent à une divulgation claire des efforts ESG, et ce retrait pourrait être perçu comme un manque d'engagement ou de progrès dans ces domaines.
-Point de surveillance : Surveiller les futures divulgations pour évaluer si la banque réintroduit ces informations ou si elle modifie sa stratégie ESG, ce qui pourrait avoir des implications sur sa réputation et sa conformité aux attentes réglementaires.</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="4" t="inlineStr"/>
-      <c r="M43" s="4" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr"/>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Tableau</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Capital réglementaire, Liquidité
-Ce qui change : Un nouveau tableau a été ajouté dans la section gestion du capital, incluant des indicateurs tels que la croissance du résultat dilué par action ajusté, le RCP ajusté, le ratio de versement des dividendes ajusté, ainsi que des ratios des fonds propres et de liquidité.
-Pertinence métier : Ce changement met l'accent sur l'amélioration de la transparence et de la divulgation des performances financières ajustées et des ratios réglementaires. L'ajout de ces indicateurs permet une meilleure évaluation de la santé financière de la banque et de sa conformité aux exigences réglementaires en matière de capital et de liquidité. Cela est crucial pour les investisseurs et les régulateurs qui surveillent la stabilité financière et la gestion des risques de la banque.
-Point de surveillance : Surveiller l'impact de ces nouveaux indicateurs sur l'évaluation de la performance financière et la conformité réglementaire de la banque.</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr"/>
-      <c r="M44" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui
+Sujet détecté : Structure du rapport, Capital réglementaire
+Ce qui change : Un nouveau tableau a été ajouté dans la section capital_management, présentant des indicateurs pour le Crédit, le Marché, l'Opérationnel et le Total.
+Pertinence métier : Ce changement met l'accent sur la transparence accrue dans la gestion du capital de la banque. L'ajout de ce tableau permet une meilleure compréhension des composantes du capital réglementaire, ce qui est crucial pour les attentes prudentielles et la comparabilité entre pairs. Cela pourrait également indiquer une réponse aux exigences réglementaires croissantes en matière de divulgation.
+Point de surveillance : Surveiller l'impact de cette nouvelle divulgation sur la perception des investisseurs et des régulateurs, ainsi que son alignement avec les attentes réglementaires en matière de capital.</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M44"/>
+  <autoFilter ref="A1:M38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T22:01:44.298197+00:00</t>
+          <t>2026-06-25T15:05:36.772173+00:00</t>
         </is>
       </c>
     </row>
@@ -1058,16 +1058,8 @@
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-24T22:01:45.441911+00:00</t>
-        </is>
-      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1180,8 +1172,16 @@
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-25T15:06:25.606724+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1235,8 +1235,16 @@
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-25T15:06:35.614092+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1840,8 +1848,16 @@
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-25T15:06:40.368064+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -2339,8 +2355,16 @@
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr"/>
-      <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25T15:06:13.224370+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2480,8 +2504,16 @@
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="4" t="inlineStr"/>
-      <c r="M36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25T15:06:08.762819+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">

--- a/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Page T1</t>
+          <t>Page (trimestre précédent)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Page T2</t>
+          <t>Page (trimestre courant)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -508,12 +508,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Libellé T1</t>
+          <t>Libellé (trimestre précédent)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Libellé T2</t>
+          <t>Libellé (trimestre courant)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -581,11 +581,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Liquidité et structure du rapport
-Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées.
-Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption.
-Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées. Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption. Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -601,7 +597,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:05:36.772173+00:00</t>
+          <t>2026-07-30T05:52:10.648561+00:00</t>
         </is>
       </c>
     </row>
@@ -648,11 +644,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
-Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
-Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -703,11 +695,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
-Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
-Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -762,11 +750,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>NON — Nouvel élément à surveiller : Non
-Sujet détecté : Reformulation sans nouveau fond
-Ce qui change : La note a été modifiée de 'Une révision en profondeur incluant des données plus récentes est en cours de va' à 'Une révision en profondeur incluant des données plus récentes a récemment été ap'.
-Pertinence métier : Ce changement est une simple reformulation de la note sans ajout de contenu substantiel ou de nouvelle information réglementaire. Il n'affecte pas la substance de la divulgation ni ne modifie la posture de la banque en matière de gestion des risques.
-Point de surveillance : Aucun point de surveillance requis car il s'agit d'une reformulation sans impact sur les attentes réglementaires ou la gestion des risques.</t>
+          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Reformulation sans nouveau fond Ce qui change : La note a été modifiée de 'Une révision en profondeur incluant des données plus récentes est en cours de va' à 'Une révision en profondeur incluant des données plus récentes a récemment été ap'. Pertinence métier : Ce changement est une simple reformulation de la note sans ajout de contenu substantiel ou de nouvelle information réglementaire. Il n'affecte pas la substance de la divulgation ni ne modifie la posture de la banque en matière de gestion des risques. Point de surveillance : Aucun point de surveillance requis car il s'agit d'une reformulation sans impact sur les attentes réglementaires ou la gestion des risques.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -821,11 +805,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
-Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
-Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
-Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -880,11 +860,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
-Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
-Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
-Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -935,11 +911,7 @@
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
-Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
-Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
-Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -990,11 +962,7 @@
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
-Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
-Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
-Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1045,11 +1013,7 @@
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Liquidité et structure du rapport
-Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées.
-Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption.
-Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées. Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption. Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1100,11 +1064,7 @@
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Liquidité et structure du rapport
-Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées.
-Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption.
-Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées. Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption. Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1159,11 +1119,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>NON — Nouvel élément à surveiller : Non
-Sujet détecté : Aucune modification substantielle
-Ce qui change : La note de bas de tableau a été reformulée sans changement de fond, avec une phrase identique à celle du rapport précédent.
-Pertinence métier : Ce changement n'apporte aucune nouvelle information ou modification substantielle à la divulgation existante. Il s'agit d'une reformulation sans impact sur la compréhension ou la gestion des risques de liquidité.
-Point de surveillance : Aucun point de surveillance requis, car il n'y a pas de changement substantiel à analyser.</t>
+          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Aucune modification substantielle Ce qui change : La note de bas de tableau a été reformulée sans changement de fond, avec une phrase identique à celle du rapport précédent. Pertinence métier : Ce changement n'apporte aucune nouvelle information ou modification substantielle à la divulgation existante. Il s'agit d'une reformulation sans impact sur la compréhension ou la gestion des risques de liquidité. Point de surveillance : Aucun point de surveillance requis, car il n'y a pas de changement substantiel à analyser.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1172,16 +1128,8 @@
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-25T15:06:25.606724+00:00</t>
-        </is>
-      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1222,11 +1170,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Texte de risque modifié
-Ce qui change : La note de S&amp;P Global Ratings a été révisée à la hausse pour la dette à long terme de premier rang, tandis que la mention de Moody's concernant la révision à la hausse a été supprimée.
-Pertinence métier : Ce changement met en évidence une modification dans la perception du risque de crédit de la banque par les agences de notation. Une révision à la hausse par S&amp;P peut indiquer une amélioration de la situation financière ou de la gestion des risques de la banque, ce qui est crucial pour les investisseurs et les régulateurs. La suppression de la mention de Moody's pourrait également signaler un changement dans l'évaluation des risques ou des attentes du marché.
-Point de surveillance : Surveiller l'impact de ces changements de notation sur la perception du risque de crédit de la banque et ses implications pour le coût du financement et la conformité réglementaire.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié Ce qui change : La note de S&amp;P Global Ratings a été révisée à la hausse pour la dette à long terme de premier rang, tandis que la mention de Moody's concernant la révision à la hausse a été supprimée. Pertinence métier : Ce changement met en évidence une modification dans la perception du risque de crédit de la banque par les agences de notation. Une révision à la hausse par S&amp;P peut indiquer une amélioration de la situation financière ou de la gestion des risques de la banque, ce qui est crucial pour les investisseurs et les régulateurs. La suppression de la mention de Moody's pourrait également signaler un changement dans l'évaluation des risques ou des attentes du marché. Point de surveillance : Surveiller l'impact de ces changements de notation sur la perception du risque de crédit de la banque et ses implications pour le coût du financement et la conformité réglementaire.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1235,16 +1179,8 @@
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-25T15:06:35.614092+00:00</t>
-        </is>
-      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1285,11 +1221,7 @@
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Texte de risque modifié
-Ce qui change : La note de S&amp;P Global Ratings a été révisée à la hausse pour la dette à long terme de premier rang, tandis que la mention de Moody's concernant la révision à la hausse a été supprimée.
-Pertinence métier : Ce changement met en évidence une modification dans la perception du risque de crédit de la banque par les agences de notation. Une révision à la hausse par S&amp;P peut indiquer une amélioration de la situation financière ou de la gestion des risques de la banque, ce qui est crucial pour les investisseurs et les régulateurs. La suppression de la mention de Moody's pourrait également signaler un changement dans l'évaluation des risques ou des attentes du marché.
-Point de surveillance : Surveiller l'impact de ces changements de notation sur la perception du risque de crédit de la banque et ses implications pour le coût du financement et la conformité réglementaire.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié Ce qui change : La note de S&amp;P Global Ratings a été révisée à la hausse pour la dette à long terme de premier rang, tandis que la mention de Moody's concernant la révision à la hausse a été supprimée. Pertinence métier : Ce changement met en évidence une modification dans la perception du risque de crédit de la banque par les agences de notation. Une révision à la hausse par S&amp;P peut indiquer une amélioration de la situation financière ou de la gestion des risques de la banque, ce qui est crucial pour les investisseurs et les régulateurs. La suppression de la mention de Moody's pourrait également signaler un changement dans l'évaluation des risques ou des attentes du marché. Point de surveillance : Surveiller l'impact de ces changements de notation sur la perception du risque de crédit de la banque et ses implications pour le coût du financement et la conformité réglementaire.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1340,11 +1272,7 @@
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information retirée
-Ce qui change : L'indicateur 'Participations dans des entreprises associées et des coentreprises' a été supprimé du tableau 'Sommaire des actifs grevés et non grevés'.
-Pertinence métier : Ce changement met en évidence une modification dans la structure de la divulgation des actifs grevés et non grevés. La suppression de cet indicateur peut affecter la transparence et la comparabilité des informations sur les actifs de la banque, ce qui est crucial pour les investisseurs et les régulateurs qui surveillent l'exposition et la gestion des actifs.
-Point de surveillance : Surveiller l'impact de cette suppression sur la compréhension des actifs grevés et non grevés, et évaluer si cela affecte la conformité aux attentes de divulgation réglementaire.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Information retirée Ce qui change : L'indicateur 'Participations dans des entreprises associées et des coentreprises' a été supprimé du tableau 'Sommaire des actifs grevés et non grevés'. Pertinence métier : Ce changement met en évidence une modification dans la structure de la divulgation des actifs grevés et non grevés. La suppression de cet indicateur peut affecter la transparence et la comparabilité des informations sur les actifs de la banque, ce qui est crucial pour les investisseurs et les régulateurs qui surveillent l'exposition et la gestion des actifs. Point de surveillance : Surveiller l'impact de cette suppression sur la compréhension des actifs grevés et non grevés, et évaluer si cela affecte la conformité aux attentes de divulgation réglementaire.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1395,11 +1323,7 @@
       <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
-Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
-Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1450,11 +1374,7 @@
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
-Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
-Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1505,11 +1425,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Capital réglementaire
-Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres.
-Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement.
-Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres. Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement. Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1560,11 +1476,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Capital réglementaire
-Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres.
-Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement.
-Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres. Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement. Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1615,11 +1527,7 @@
       <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Capital réglementaire
-Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres.
-Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement.
-Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres. Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement. Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1670,11 +1578,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Capital réglementaire
-Ce qui change : Une note a été ajoutée indiquant que les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.
-Pertinence métier : Ce changement met l'accent sur l'impact des opérations de rachat sur le capital réglementaire de la banque. Le rachat des BCRL - Série 1 peut affecter la composition des fonds propres réglementaires, ce qui est crucial pour la conformité aux exigences de capital. Cela souligne l'importance de surveiller les ajustements dans la structure du capital qui peuvent influencer les ratios prudentiels et la capacité de la banque à répondre aux attentes réglementaires.
-Point de surveillance : Surveiller l'impact du rachat des BCRL - Série 1 sur les ratios de capital et la conformité aux exigences réglementaires, en particulier en ce qui concerne le TLAC et le ratio de levier.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : Une note a été ajoutée indiquant que les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025. Pertinence métier : Ce changement met l'accent sur l'impact des opérations de rachat sur le capital réglementaire de la banque. Le rachat des BCRL - Série 1 peut affecter la composition des fonds propres réglementaires, ce qui est crucial pour la conformité aux exigences de capital. Cela souligne l'importance de surveiller les ajustements dans la structure du capital qui peuvent influencer les ratios prudentiels et la capacité de la banque à répondre aux attentes réglementaires. Point de surveillance : Surveiller l'impact du rachat des BCRL - Série 1 sur les ratios de capital et la conformité aux exigences réglementaires, en particulier en ce qui concerne le TLAC et le ratio de levier.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1725,11 +1629,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Exigences réglementaires ou conformité, Ratio ou seuil prudentiel
-Ce qui change : La note modifiée indique un changement de date concernant la confirmation par le BSIF de la réserve pour stabilité intérieure, passant du 18 juin 2024 au 26 juin 2025. De plus, une nouvelle note mentionne que les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.
-Pertinence métier : Ce changement met en évidence une mise à jour des exigences réglementaires et des ratios prudentiels, ce qui est crucial pour la conformité et la gestion des fonds propres de la banque. La modification de la date de confirmation par le BSIF peut indiquer un ajustement dans les attentes réglementaires, tandis que la prise en compte du rachat des BCRL dans les ratios souligne l'impact des décisions de financement sur les exigences de capital.
-Point de surveillance : Surveiller l'impact de ces changements sur les ratios de fonds propres et la conformité aux exigences du BSIF, ainsi que l'effet du rachat des BCRL sur la structure de capital.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Exigences réglementaires ou conformité, Ratio ou seuil prudentiel Ce qui change : La note modifiée indique un changement de date concernant la confirmation par le BSIF de la réserve pour stabilité intérieure, passant du 18 juin 2024 au 26 juin 2025. De plus, une nouvelle note mentionne que les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025. Pertinence métier : Ce changement met en évidence une mise à jour des exigences réglementaires et des ratios prudentiels, ce qui est crucial pour la conformité et la gestion des fonds propres de la banque. La modification de la date de confirmation par le BSIF peut indiquer un ajustement dans les attentes réglementaires, tandis que la prise en compte du rachat des BCRL dans les ratios souligne l'impact des décisions de financement sur les exigences de capital. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de fonds propres et la conformité aux exigences du BSIF, ainsi que l'effet du rachat des BCRL sur la structure de capital.</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1780,11 +1680,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Méthode de calcul ou approche modifiée
-Ce qui change : Inclusion de CWB dans le calcul du risque opérationnel au cours du deuxième trimestre de 2025.
-Pertinence métier : Ce changement met l'accent sur une modification méthodologique dans le calcul du risque opérationnel, ce qui peut avoir un impact sur les exigences de capital réglementaire de la banque. L'inclusion de CWB pourrait modifier la pondération des actifs en fonction des risques, influençant ainsi les ratios de capital réglementaire. Cela est crucial pour la conformité aux attentes prudentielles et pour la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de l'inclusion de CWB sur les ratios de capital et s'assurer que la banque reste conforme aux exigences réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée Ce qui change : Inclusion de CWB dans le calcul du risque opérationnel au cours du deuxième trimestre de 2025. Pertinence métier : Ce changement met l'accent sur une modification méthodologique dans le calcul du risque opérationnel, ce qui peut avoir un impact sur les exigences de capital réglementaire de la banque. L'inclusion de CWB pourrait modifier la pondération des actifs en fonction des risques, influençant ainsi les ratios de capital réglementaire. Cela est crucial pour la conformité aux attentes prudentielles et pour la comparabilité entre pairs. Point de surveillance : Surveiller l'impact de l'inclusion de CWB sur les ratios de capital et s'assurer que la banque reste conforme aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1835,11 +1731,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Fonds propres réglementaires, Structure du rapport
-Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025.
-Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres.
-Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Structure du rapport Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025. Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres. Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1848,16 +1740,8 @@
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-25T15:06:40.368064+00:00</t>
-        </is>
-      </c>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1898,11 +1782,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Fonds propres réglementaires, Structure du rapport
-Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025.
-Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres.
-Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Structure du rapport Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025. Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres. Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1957,11 +1837,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Fonds propres réglementaires, Structure du rapport
-Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025.
-Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres.
-Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Structure du rapport Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025. Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres. Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2012,11 +1888,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
-Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
-Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
-Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2071,11 +1943,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
-Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
-Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
-Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2126,11 +1994,7 @@
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée
-Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés.
-Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires.
-Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2181,11 +2045,7 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
-Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
-Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2236,11 +2096,7 @@
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Texte de risque modifié
-Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion.
-Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel.
-Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2295,11 +2151,7 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Exigences réglementaires ou conformité, Ratio ou seuil prudentiel
-Ce qui change : La note modifiée indique un changement de date concernant la confirmation par le BSIF de la réserve pour stabilité intérieure, passant du 18 juin 2024 au 26 juin 2025. De plus, une nouvelle note mentionne que les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.
-Pertinence métier : Ce changement met en évidence une mise à jour des exigences réglementaires et des ratios prudentiels, ce qui est crucial pour la conformité et la gestion des fonds propres de la banque. La modification de la date de confirmation par le BSIF peut indiquer un ajustement dans les attentes réglementaires, tandis que la prise en compte du rachat des BCRL dans les ratios souligne l'impact des décisions de financement sur les exigences de capital.
-Point de surveillance : Surveiller l'impact de ces changements sur les ratios de fonds propres et la conformité aux exigences du BSIF, ainsi que l'effet du rachat des BCRL sur la structure de capital.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Exigences réglementaires ou conformité, Ratio ou seuil prudentiel Ce qui change : La note modifiée indique un changement de date concernant la confirmation par le BSIF de la réserve pour stabilité intérieure, passant du 18 juin 2024 au 26 juin 2025. De plus, une nouvelle note mentionne que les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025. Pertinence métier : Ce changement met en évidence une mise à jour des exigences réglementaires et des ratios prudentiels, ce qui est crucial pour la conformité et la gestion des fonds propres de la banque. La modification de la date de confirmation par le BSIF peut indiquer un ajustement dans les attentes réglementaires, tandis que la prise en compte du rachat des BCRL dans les ratios souligne l'impact des décisions de financement sur les exigences de capital. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de fonds propres et la conformité aux exigences du BSIF, ainsi que l'effet du rachat des BCRL sur la structure de capital.</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2342,11 +2194,7 @@
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée, Gouvernance des risques
-Ce qui change : Un nouveau tableau a été ajouté dans la section gestion des risques, listant divers types de risques, y compris le risque de non-conformité à la réglementation et le risque environnemental et social.
-Pertinence métier : Ce changement met l'accent sur une approche plus holistique de la gestion des risques en incluant une gamme étendue de risques, tels que le risque environnemental et social, qui sont de plus en plus pertinents dans le contexte actuel de réglementation accrue et de préoccupations ESG. Cela reflète une volonté de la banque de renforcer sa gouvernance des risques en intégrant des facteurs de risque plus diversifiés.
-Point de surveillance : Surveiller comment cette nouvelle divulgation influence la stratégie de gestion des risques de la banque et si elle entraîne des ajustements dans les processus de gouvernance des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Information ajoutée, Gouvernance des risques Ce qui change : Un nouveau tableau a été ajouté dans la section gestion des risques, listant divers types de risques, y compris le risque de non-conformité à la réglementation et le risque environnemental et social. Pertinence métier : Ce changement met l'accent sur une approche plus holistique de la gestion des risques en incluant une gamme étendue de risques, tels que le risque environnemental et social, qui sont de plus en plus pertinents dans le contexte actuel de réglementation accrue et de préoccupations ESG. Cela reflète une volonté de la banque de renforcer sa gouvernance des risques en intégrant des facteurs de risque plus diversifiés. Point de surveillance : Surveiller comment cette nouvelle divulgation influence la stratégie de gestion des risques de la banque et si elle entraîne des ajustements dans les processus de gouvernance des risques.</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2355,16 +2203,8 @@
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr"/>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-25T15:06:13.224370+00:00</t>
-        </is>
-      </c>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2397,11 +2237,7 @@
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information retirée, Risque émergent : cybersécurité
-Ce qui change : Le tableau concernant les indicateurs de sécurité de l'information a été supprimé dans le rapport courant.
-Pertinence métier : Ce changement met en évidence une potentielle réduction de la transparence sur la gestion des risques liés à la cybersécurité. La sécurité de l'information est un domaine critique, surtout avec l'augmentation des cyberattaques. La suppression de ce tableau pourrait indiquer un changement de posture ou une réévaluation de la manière dont ces informations sont communiquées aux parties prenantes.
-Point de surveillance : Il est crucial de surveiller si cette suppression est compensée par d'autres formes de divulgation ou si elle reflète un changement dans la gestion des risques de cybersécurité.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Information retirée, Risque émergent : cybersécurité Ce qui change : Le tableau concernant les indicateurs de sécurité de l'information a été supprimé dans le rapport courant. Pertinence métier : Ce changement met en évidence une potentielle réduction de la transparence sur la gestion des risques liés à la cybersécurité. La sécurité de l'information est un domaine critique, surtout avec l'augmentation des cyberattaques. La suppression de ce tableau pourrait indiquer un changement de posture ou une réévaluation de la manière dont ces informations sont communiquées aux parties prenantes. Point de surveillance : Il est crucial de surveiller si cette suppression est compensée par d'autres formes de divulgation ou si elle reflète un changement dans la gestion des risques de cybersécurité.</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2444,11 +2280,7 @@
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Information ajoutée
-Ce qui change : Un nouveau tableau a été ajouté dans la section gestion du capital, présentant des indicateurs pour le crédit, le marché, l'opérationnel, et d'autres risques, ainsi qu'un total.
-Pertinence métier : Ce changement met en évidence une nouvelle approche de la banque pour divulguer des informations sur la gestion du capital. L'ajout de ce tableau pourrait indiquer une volonté de transparence accrue ou une réponse à des attentes réglementaires spécifiques concernant la gestion des risques et du capital. Cela permet une meilleure comparabilité entre pairs et peut refléter une adaptation aux exigences prudentielles.
-Point de surveillance : Surveiller si ce tableau est lié à de nouvelles exigences réglementaires ou à une modification de la stratégie de gestion du capital de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Information ajoutée Ce qui change : Un nouveau tableau a été ajouté dans la section gestion du capital, présentant des indicateurs pour le crédit, le marché, l'opérationnel, et d'autres risques, ainsi qu'un total. Pertinence métier : Ce changement met en évidence une nouvelle approche de la banque pour divulguer des informations sur la gestion du capital. L'ajout de ce tableau pourrait indiquer une volonté de transparence accrue ou une réponse à des attentes réglementaires spécifiques concernant la gestion des risques et du capital. Cela permet une meilleure comparabilité entre pairs et peut refléter une adaptation aux exigences prudentielles. Point de surveillance : Surveiller si ce tableau est lié à de nouvelles exigences réglementaires ou à une modification de la stratégie de gestion du capital de la banque.</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2491,11 +2323,7 @@
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Capital réglementaire
-Ce qui change : Un nouveau tableau a été ajouté dans la section capital_management, présentant des indicateurs pour le Crédit, le Marché, l'Opérationnel et le Total.
-Pertinence métier : Ce changement met l'accent sur la transparence accrue dans la gestion du capital de la banque. L'ajout de ce tableau permet une meilleure compréhension des composantes du capital réglementaire, ce qui est crucial pour la conformité aux exigences prudentielles et pour la comparabilité entre pairs.
-Point de surveillance : Surveiller l'impact de ce nouveau tableau sur la divulgation des ratios de capital et s'assurer qu'il est aligné avec les attentes réglementaires en matière de transparence et de gestion du capital.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : Un nouveau tableau a été ajouté dans la section capital_management, présentant des indicateurs pour le Crédit, le Marché, l'Opérationnel et le Total. Pertinence métier : Ce changement met l'accent sur la transparence accrue dans la gestion du capital de la banque. L'ajout de ce tableau permet une meilleure compréhension des composantes du capital réglementaire, ce qui est crucial pour la conformité aux exigences prudentielles et pour la comparabilité entre pairs. Point de surveillance : Surveiller l'impact de ce nouveau tableau sur la divulgation des ratios de capital et s'assurer qu'il est aligné avec les attentes réglementaires en matière de transparence et de gestion du capital.</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2504,16 +2332,8 @@
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-25T15:06:08.762819+00:00</t>
-        </is>
-      </c>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -2546,11 +2366,7 @@
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Capital réglementaire
-Ce qui change : Un nouveau tableau a été ajouté dans la section gestion du capital, présentant des indicateurs pour le crédit, le marché, l'opérationnel et le total.
-Pertinence métier : Ce changement met en évidence une nouvelle approche de la banque pour divulguer des informations sur ses indicateurs de capital. Cela pourrait refléter une réponse aux attentes réglementaires accrues en matière de transparence et de gestion des risques. La présentation de ces indicateurs est cruciale pour évaluer la santé financière de la banque et sa conformité aux exigences de capital réglementaire.
-Point de surveillance : Surveiller comment ces indicateurs influencent la gestion du capital et la conformité réglementaire de la banque, ainsi que toute mise à jour future de la méthodologie de calcul ou de présentation.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : Un nouveau tableau a été ajouté dans la section gestion du capital, présentant des indicateurs pour le crédit, le marché, l'opérationnel et le total. Pertinence métier : Ce changement met en évidence une nouvelle approche de la banque pour divulguer des informations sur ses indicateurs de capital. Cela pourrait refléter une réponse aux attentes réglementaires accrues en matière de transparence et de gestion des risques. La présentation de ces indicateurs est cruciale pour évaluer la santé financière de la banque et sa conformité aux exigences de capital réglementaire. Point de surveillance : Surveiller comment ces indicateurs influencent la gestion du capital et la conformité réglementaire de la banque, ainsi que toute mise à jour future de la méthodologie de calcul ou de présentation.</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2593,11 +2409,7 @@
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui
-Sujet détecté : Structure du rapport, Capital réglementaire
-Ce qui change : Un nouveau tableau a été ajouté dans la section capital_management, présentant des indicateurs pour le Crédit, le Marché, l'Opérationnel et le Total.
-Pertinence métier : Ce changement met l'accent sur la transparence accrue dans la gestion du capital de la banque. L'ajout de ce tableau permet une meilleure compréhension des composantes du capital réglementaire, ce qui est crucial pour les attentes prudentielles et la comparabilité entre pairs. Cela pourrait également indiquer une réponse aux exigences réglementaires croissantes en matière de divulgation.
-Point de surveillance : Surveiller l'impact de cette nouvelle divulgation sur la perception des investisseurs et des régulateurs, ainsi que son alignement avec les attentes réglementaires en matière de capital.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : Un nouveau tableau a été ajouté dans la section capital_management, présentant des indicateurs pour le Crédit, le Marché, l'Opérationnel et le Total. Pertinence métier : Ce changement met l'accent sur la transparence accrue dans la gestion du capital de la banque. L'ajout de ce tableau permet une meilleure compréhension des composantes du capital réglementaire, ce qui est crucial pour les attentes prudentielles et la comparabilité entre pairs. Cela pourrait également indiquer une réponse aux exigences réglementaires croissantes en matière de divulgation. Point de surveillance : Surveiller l'impact de cette nouvelle divulgation sur la perception des investisseurs et des régulateurs, ainsi que son alignement avec les attentes réglementaires en matière de capital.</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">

--- a/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30T05:52:10.648561+00:00</t>
+          <t>2026-07-30T06:31:21.237102+00:00</t>
         </is>
       </c>
     </row>
@@ -1022,8 +1022,16 @@
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30T06:31:21.935771+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">

--- a/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -550,56 +550,52 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>Exigences de déclaration relatives au ratio de liquidité à long terme (1) (2) *</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>(3) Les valeurs pondérées sont calculées après l’application des pondérations prescrites par la ligne directrice NI du BSIF.</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Ratio de liquidité à court terme</t>
+          <t>(3) Les valeurs pondérées sont calculées après l’application des pondérations prescrites par la ligne directrice NL du BSIF.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées. Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption. Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
+          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Texte de risque modifié Ce qui change : BNC modifie une note de bas de tableau sans changement substantiel de contenu. Pertinence métier : Ce changement est purement cosmétique et n'affecte pas la substance de la divulgation. Il s'agit d'une reformulation sans impact sur la compréhension ou la gestion des risques de liquidité. Aucune nouvelle information n'est introduite, et la modification n'a pas d'incidence sur la transparence ou la comparabilité des pratiques de gestion des risques de la banque. Point de surveillance : Aucun point de surveillance particulier n'est requis pour cette modification cosmétique.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-30T06:31:21.237102+00:00</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -644,7 +640,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -695,7 +691,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -750,7 +746,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Reformulation sans nouveau fond Ce qui change : La note a été modifiée de 'Une révision en profondeur incluant des données plus récentes est en cours de va' à 'Une révision en profondeur incluant des données plus récentes a récemment été ap'. Pertinence métier : Ce changement est une simple reformulation de la note sans ajout de contenu substantiel ou de nouvelle information réglementaire. Il n'affecte pas la substance de la divulgation ni ne modifie la posture de la banque en matière de gestion des risques. Point de surveillance : Aucun point de surveillance requis car il s'agit d'une reformulation sans impact sur les attentes réglementaires ou la gestion des risques.</t>
+          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Texte de risque modifié Ce qui change : BNC modifie une note de bas de tableau en changeant le temps verbal de 'est en cours de va' à 'a récemment été ap'. Pertinence métier : Ce changement est purement cosmétique et n'affecte pas la substance de la divulgation. Il s'agit d'une simple correction de formulation qui ne modifie ni les risques, ni la gouvernance, ni les exigences réglementaires. La modification n'introduit pas de nouvelle information ni ne change la posture de la banque en matière de gestion des risques. Point de surveillance : Aucun point de surveillance particulier n'est requis pour ce changement, car il n'affecte pas la gestion des risques ou la conformité réglementaire.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -805,7 +801,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -845,22 +841,18 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Renommage</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Prêts et acceptations, déduction faite des provisions</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Prêts, déduction faite des provisions</t>
-        </is>
-      </c>
+          <t>Acceptations</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -869,8 +861,16 @@
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30T22:24:17.096512+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -905,13 +905,13 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Acceptations</t>
+          <t>Positions liées aux activités de négociation pour lesquelles la mesure du risque est la VaR totale. Pour de plus amples renseignements, se reporter au tableau illustrant la distribution de la VaR des portefeuilles de négociation par catégorie de risque et leur effet de diversification présenté à la page suivante.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -936,17 +936,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -956,13 +956,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Positions liées aux activités de négociation pour lesquelles la mesure du risque est la VaR totale. Pour de plus amples renseignements, se reporter au tableau illustrant la distribution de la VaR des portefeuilles de négociation par catégorie de risque et leur effet de diversification présenté à la page suivante.</t>
+          <t>Participations dans des entreprises associées et des coentreprises</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée Ce qui change : BNC modifie les indicateurs en supprimant les participations dans des entreprises associées et des coentreprises, et en renommant les prêts et acceptations, déduction faite des provisions, en prêts, déduction faite des provisions. De plus, certaines notes ont été supprimées en raison de modifications de méthodes comptables liées à l'adoption de l'IFRS 17. Pertinence métier : Ce changement met en évidence une révision des méthodes comptables et des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières de la BNC. L'adoption de l'IFRS 17 pourrait avoir des implications sur la manière dont les actifs et passifs sont évalués, influençant ainsi la perception des risques financiers et la gestion des fonds propres. Cela pourrait également impacter la manière dont la BNC communique ses risques aux investisseurs et aux régulateurs. Point de surveillance : Surveiller l'impact de l'adoption de l'IFRS 17 sur les rapports financiers et la gestion des risques de la BNC.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1007,13 +1007,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Participations dans des entreprises associées et des coentreprises</t>
+          <t>Certains montants ont été ajustés à la suite de modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées. Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption. Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée Ce qui change : BNC modifie les indicateurs en supprimant les participations dans des entreprises associées et des coentreprises, et en renommant les prêts et acceptations, déduction faite des provisions, en prêts, déduction faite des provisions. De plus, certaines notes ont été supprimées en raison de modifications de méthodes comptables liées à l'adoption de l'IFRS 17. Pertinence métier : Ce changement met en évidence une révision des méthodes comptables et des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières de la BNC. L'adoption de l'IFRS 17 pourrait avoir des implications sur la manière dont les actifs et passifs sont évalués, influençant ainsi la perception des risques financiers et la gestion des fonds propres. Cela pourrait également impacter la manière dont la BNC communique ses risques aux investisseurs et aux régulateurs. Point de surveillance : Surveiller l'impact de l'adoption de l'IFRS 17 sur les rapports financiers et la gestion des risques de la BNC.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1022,16 +1022,8 @@
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-30T06:31:21.935771+00:00</t>
-        </is>
-      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1041,22 +1033,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>Exposition maximale au risque de crédit selon les catégories d’actifs de Bâle (1) *</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1066,13 +1058,13 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Certains montants ont été ajustés à la suite de modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
+          <t>Particuliers – Total</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Liquidité et structure du rapport Ce qui change : Un nouvel indicateur, le Ratio de liquidité à court terme, a été ajouté, tandis que les indicateurs sur les participations dans des entreprises associées et des coentreprises ont été supprimés. De plus, des notes concernant des ajustements liés à l'IFRS 17 ont été retirées. Pertinence métier : Ce changement met l'accent sur l'importance accrue accordée à la liquidité à court terme, un aspect crucial pour la gestion des risques financiers et la conformité réglementaire. L'ajout de cet indicateur reflète une attention particulière aux exigences de liquidité, ce qui est essentiel pour la stabilité financière de la banque. La suppression des notes sur l'IFRS 17 pourrait indiquer une stabilisation des méthodes comptables après leur adoption. Point de surveillance : Surveiller l'impact de l'ajout du Ratio de liquidité à court terme sur les pratiques de gestion des risques et la conformité aux exigences réglementaires en matière de liquidité.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Ratio ou seuil prudentiel Ce qui change : BNC supprime plusieurs indicateurs clés du tableau d'exposition maximale au risque de crédit, notamment les totaux pour les catégories Particuliers, Autres que particuliers, Portefeuille de négociation et Titrisation. Pertinence métier : Ce changement met en évidence une modification substantielle dans la manière dont la BNC présente son exposition au risque de crédit. La suppression de ces indicateurs pourrait affecter la transparence et la comparabilité des risques de crédit de la banque par rapport à ses pairs, en particulier en ce qui concerne les ratios réglementaires et les exigences de Bâle. Cela pourrait également influencer la perception des investisseurs et des régulateurs sur la gestion des risques de crédit de la banque. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des divulgations de risque de crédit et la conformité aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1092,47 +1084,43 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Exigences de déclaration relatives au ratio de liquidité à long terme (1) (2) *</t>
+          <t>Exposition maximale au risque de crédit selon les catégories d’actifs de Bâle (1) *</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Les valeurs pondérées sont calculées après l’application des pondérations prescrites par la ligne directrice NI du BSIF.</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Les valeurs pondérées sont calculées après l’application des pondérations prescrites par la ligne directrice NL du BSIF.</t>
-        </is>
-      </c>
+          <t>Autres que particuliers – Total</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Aucune modification substantielle Ce qui change : La note de bas de tableau a été reformulée sans changement de fond, avec une phrase identique à celle du rapport précédent. Pertinence métier : Ce changement n'apporte aucune nouvelle information ou modification substantielle à la divulgation existante. Il s'agit d'une reformulation sans impact sur la compréhension ou la gestion des risques de liquidité. Point de surveillance : Aucun point de surveillance requis, car il n'y a pas de changement substantiel à analyser.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Ratio ou seuil prudentiel Ce qui change : BNC supprime plusieurs indicateurs clés du tableau d'exposition maximale au risque de crédit, notamment les totaux pour les catégories Particuliers, Autres que particuliers, Portefeuille de négociation et Titrisation. Pertinence métier : Ce changement met en évidence une modification substantielle dans la manière dont la BNC présente son exposition au risque de crédit. La suppression de ces indicateurs pourrait affecter la transparence et la comparabilité des risques de crédit de la banque par rapport à ses pairs, en particulier en ce qui concerne les ratios réglementaires et les exigences de Bâle. Cela pourrait également influencer la perception des investisseurs et des régulateurs sur la gestion des risques de crédit de la banque. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des divulgations de risque de crédit et la conformité aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
@@ -1147,38 +1135,38 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Notations de crédit de la Banque</t>
+          <t>Exposition maximale au risque de crédit selon les catégories d’actifs de Bâle (1) *</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Le 17 octobre 2025, S&amp;P Global Ratings (S&amp;P) a révisé à la hausse la notation de la dette à long terme de premier rang non assujettie au régime de recapitalisation interne des banques, la dette à long terme de premier rang, la dette subordonnée FPUNV, les billets de capital à recours limité FPUNV et les actions privilégiées FPUNV de la Banque.</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Portefeuille de négociation – Total</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié Ce qui change : La note de S&amp;P Global Ratings a été révisée à la hausse pour la dette à long terme de premier rang, tandis que la mention de Moody's concernant la révision à la hausse a été supprimée. Pertinence métier : Ce changement met en évidence une modification dans la perception du risque de crédit de la banque par les agences de notation. Une révision à la hausse par S&amp;P peut indiquer une amélioration de la situation financière ou de la gestion des risques de la banque, ce qui est crucial pour les investisseurs et les régulateurs. La suppression de la mention de Moody's pourrait également signaler un changement dans l'évaluation des risques ou des attentes du marché. Point de surveillance : Surveiller l'impact de ces changements de notation sur la perception du risque de crédit de la banque et ses implications pour le coût du financement et la conformité réglementaire.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Ratio ou seuil prudentiel Ce qui change : BNC supprime plusieurs indicateurs clés du tableau d'exposition maximale au risque de crédit, notamment les totaux pour les catégories Particuliers, Autres que particuliers, Portefeuille de négociation et Titrisation. Pertinence métier : Ce changement met en évidence une modification substantielle dans la manière dont la BNC présente son exposition au risque de crédit. La suppression de ces indicateurs pourrait affecter la transparence et la comparabilité des risques de crédit de la banque par rapport à ses pairs, en particulier en ce qui concerne les ratios réglementaires et les exigences de Bâle. Cela pourrait également influencer la perception des investisseurs et des régulateurs sur la gestion des risques de crédit de la banque. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des divulgations de risque de crédit et la conformité aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1198,22 +1186,22 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Notations de crédit de la Banque</t>
+          <t>Exposition maximale au risque de crédit selon les catégories d’actifs de Bâle (1) *</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1223,13 +1211,13 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Le 24 septembre 2024, Moody's a placé sous révision en vue d’une révision à la hausse toutes les notations et évaluations à long terme de la Banque, y compris son évaluation de crédit de base Baa1, les notations de dépôts à long terme Aa3 et les notations de risque de contrepartie, ainsi que son évaluation de risque de contrepartie de Aa3(cr).</t>
+          <t>Titrisation – Total</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié Ce qui change : La note de S&amp;P Global Ratings a été révisée à la hausse pour la dette à long terme de premier rang, tandis que la mention de Moody's concernant la révision à la hausse a été supprimée. Pertinence métier : Ce changement met en évidence une modification dans la perception du risque de crédit de la banque par les agences de notation. Une révision à la hausse par S&amp;P peut indiquer une amélioration de la situation financière ou de la gestion des risques de la banque, ce qui est crucial pour les investisseurs et les régulateurs. La suppression de la mention de Moody's pourrait également signaler un changement dans l'évaluation des risques ou des attentes du marché. Point de surveillance : Surveiller l'impact de ces changements de notation sur la perception du risque de crédit de la banque et ses implications pour le coût du financement et la conformité réglementaire.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Ratio ou seuil prudentiel Ce qui change : BNC supprime plusieurs indicateurs clés du tableau d'exposition maximale au risque de crédit, notamment les totaux pour les catégories Particuliers, Autres que particuliers, Portefeuille de négociation et Titrisation. Pertinence métier : Ce changement met en évidence une modification substantielle dans la manière dont la BNC présente son exposition au risque de crédit. La suppression de ces indicateurs pourrait affecter la transparence et la comparabilité des risques de crédit de la banque par rapport à ses pairs, en particulier en ce qui concerne les ratios réglementaires et les exigences de Bâle. Cela pourrait également influencer la perception des investisseurs et des régulateurs sur la gestion des risques de crédit de la banque. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des divulgations de risque de crédit et la conformité aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1249,38 +1237,38 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Sommaire des actifs grevés et non grevés (1) *</t>
+          <t>Notations de crédit de la Banque</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Participations dans des entreprises associées et des coentreprises</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Le 17 octobre 2025, S&amp;P Global Ratings (S&amp;P) a révisé à la hausse la notation de la dette à long terme de premier rang non assujettie au régime de recapitalisation interne des banques, la dette à long terme de premier rang, la dette subordonnée FPUNV, les billets de capital à recours limité FPUNV et les actions privilégiées FPUNV de la Banque.</t>
+        </is>
+      </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Information retirée Ce qui change : L'indicateur 'Participations dans des entreprises associées et des coentreprises' a été supprimé du tableau 'Sommaire des actifs grevés et non grevés'. Pertinence métier : Ce changement met en évidence une modification dans la structure de la divulgation des actifs grevés et non grevés. La suppression de cet indicateur peut affecter la transparence et la comparabilité des informations sur les actifs de la banque, ce qui est crucial pour les investisseurs et les régulateurs qui surveillent l'exposition et la gestion des actifs. Point de surveillance : Surveiller l'impact de cette suppression sur la compréhension des actifs grevés et non grevés, et évaluer si cela affecte la conformité aux attentes de divulgation réglementaire.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Facteur de risque modifié Ce qui change : BNC modifie les notations de crédit en intégrant une révision à la hausse par S&amp;P Global Ratings et en supprimant une révision par Moody's. Pertinence métier : Ce changement met en évidence une amélioration de la perception du risque de crédit de la BNC par S&amp;P, ce qui peut influencer positivement la confiance des investisseurs et réduire le coût du financement. La suppression de la révision par Moody's pourrait indiquer une stabilisation des perspectives de crédit. Cette modification affecte la transparence des notations de crédit, un élément crucial pour les parties prenantes évaluant le risque de crédit de la banque. Point de surveillance : Surveiller l'impact de ces changements de notation sur les conditions de financement et la perception du risque par les autres agences de notation.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1300,22 +1288,22 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
+          <t>Notations de crédit de la Banque</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1325,13 +1313,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Titrisation de créances sur cartes de crédit</t>
+          <t>Le 24 septembre 2024, Moody's a placé sous révision en vue d’une révision à la hausse toutes les notations et évaluations à long terme de la Banque, y compris son évaluation de crédit de base Baa1, les notations de dépôts à long terme Aa3 et les notations de risque de contrepartie, ainsi que son évaluation de risque de contrepartie de Aa3(cr).</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Facteur de risque modifié Ce qui change : BNC modifie les notations de crédit en intégrant une révision à la hausse par S&amp;P Global Ratings et en supprimant une révision par Moody's. Pertinence métier : Ce changement met en évidence une amélioration de la perception du risque de crédit de la BNC par S&amp;P, ce qui peut influencer positivement la confiance des investisseurs et réduire le coût du financement. La suppression de la révision par Moody's pourrait indiquer une stabilisation des perspectives de crédit. Cette modification affecte la transparence des notations de crédit, un élément crucial pour les parties prenantes évaluant le risque de crédit de la banque. Point de surveillance : Surveiller l'impact de ces changements de notation sur les conditions de financement et la perception du risque par les autres agences de notation.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1351,22 +1339,22 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
+          <t>Sommaire des actifs grevés et non grevés (1) *</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1376,13 +1364,13 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Les certificats de dépôt libellés en euros sont inclus dans les billets de premier rang non garantis à moyen terme.</t>
+          <t>Participations dans des entreprises associées et des coentreprises</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : BNC supprime les indicateurs relatifs aux participations dans des entreprises associées et des coentreprises du tableau Sommaire des actifs grevés et non grevés. Pertinence métier : Ce changement met en évidence une modification dans la manière dont la BNC présente ses actifs grevés et non grevés, ce qui peut affecter la transparence et la compréhension des risques associés à ces actifs. La suppression de ces indicateurs pourrait réduire la visibilité sur l'exposition de la banque à des entités associées, ce qui est crucial pour évaluer les risques de concentration et de dépendance. Cela peut également influencer la comparabilité avec d'autres institutions financières qui continuent de divulguer ces informations. Point de surveillance : Surveiller l'impact de cette suppression sur l'évaluation des risques de concentration et la transparence des rapports financiers de la BNC.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1397,22 +1385,22 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1422,18 +1410,18 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Série 47</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Titrisation de créances sur cartes de crédit</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres. Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement. Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1448,43 +1436,43 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Série 49</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Les acceptations bancaires ne sont pas incluses dans ce tableau.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres. Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement. Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1499,27 +1487,27 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1529,13 +1517,13 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Série 32</t>
+          <t>Les certificats de dépôt libellés en euros sont inclus dans les billets de premier rang non garantis à moyen terme.</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : Les indicateurs 'Série 47' et 'Série 49' ont été ajoutés, tandis que 'Série 32' a été supprimé dans le tableau des actions et autres instruments de capitaux propres. Pertinence métier : Ce changement met l'accent sur la réorganisation des instruments de capitaux propres de la banque, ce qui peut refléter une stratégie de gestion du capital modifiée. L'ajout et le retrait de séries spécifiques peuvent indiquer des ajustements dans la structure du capital, potentiellement en réponse à des exigences réglementaires ou à des stratégies internes de financement. Point de surveillance : Surveiller l'impact de ces changements sur la composition du capital réglementaire et la conformité aux exigences prudentielles.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1555,17 +1543,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Capital réglementaire (1), ratio de levier (1) et TLAC (2)</t>
+          <t>(sans titre)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1581,12 +1569,12 @@
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
+          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisée conformément à l’approche utilisée par la Banque.</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : Une note a été ajoutée indiquant que les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025. Pertinence métier : Ce changement met l'accent sur l'impact des opérations de rachat sur le capital réglementaire de la banque. Le rachat des BCRL - Série 1 peut affecter la composition des fonds propres réglementaires, ce qui est crucial pour la conformité aux exigences de capital. Cela souligne l'importance de surveiller les ajustements dans la structure du capital qui peuvent influencer les ratios prudentiels et la capacité de la banque à répondre aux attentes réglementaires. Point de surveillance : Surveiller l'impact du rachat des BCRL - Série 1 sur les ratios de capital et la conformité aux exigences réglementaires, en particulier en ce qui concerne le TLAC et le ratio de levier.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée Ce qui change : BNC modifie la méthode de calcul du risque opérationnel en incluant CWB dans ses évaluations. Pertinence métier : Ce changement met en évidence une modification dans la manière dont BNC évalue son risque opérationnel, en intégrant désormais les données de CWB. Cela peut avoir un impact significatif sur la gestion du risque opérationnel de la banque, car l'inclusion de nouvelles entités peut modifier les profils de risque et nécessiter des ajustements dans les stratégies de gestion des risques. Cette modification améliore la transparence et la précision des évaluations de risque, ce qui est crucial pour maintenir la résilience de la banque face aux risques opérationnels. Point de surveillance : Surveiller l'impact de l'inclusion de CWB sur les évaluations de risque opérationnel et les ajustements nécessaires dans les stratégies de gestion des risques.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1606,22 +1594,22 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1632,12 +1620,12 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
+          <t>Série 47</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Exigences réglementaires ou conformité, Ratio ou seuil prudentiel Ce qui change : La note modifiée indique un changement de date concernant la confirmation par le BSIF de la réserve pour stabilité intérieure, passant du 18 juin 2024 au 26 juin 2025. De plus, une nouvelle note mentionne que les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025. Pertinence métier : Ce changement met en évidence une mise à jour des exigences réglementaires et des ratios prudentiels, ce qui est crucial pour la conformité et la gestion des fonds propres de la banque. La modification de la date de confirmation par le BSIF peut indiquer un ajustement dans les attentes réglementaires, tandis que la prise en compte du rachat des BCRL dans les ratios souligne l'impact des décisions de financement sur les exigences de capital. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de fonds propres et la conformité aux exigences du BSIF, ainsi que l'effet du rachat des BCRL sur la structure de capital.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : BNC modifie le tableau des actions et autres instruments de capitaux propres en ajoutant les indicateurs Série 47 et Série 49, tout en supprimant l'indicateur Série 32. Pertinence métier : Ce changement met en évidence une réorganisation des instruments de capitaux propres de la BNC, ce qui peut affecter la composition des fonds propres réglementaires. L'ajout des Séries 47 et 49 pourrait indiquer l'émission de nouveaux instruments de capital, tandis que la suppression de la Série 32 pourrait signaler le rachat ou l'échéance d'un instrument existant. Cela a un impact direct sur la structure du capital réglementaire et la capacité de la banque à répondre aux exigences de fonds propres. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la conformité aux exigences prudentielles.</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1657,22 +1645,22 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1683,12 +1671,12 @@
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisée conformément à l’approche utilisée par la Banque.</t>
+          <t>Série 49</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée Ce qui change : Inclusion de CWB dans le calcul du risque opérationnel au cours du deuxième trimestre de 2025. Pertinence métier : Ce changement met l'accent sur une modification méthodologique dans le calcul du risque opérationnel, ce qui peut avoir un impact sur les exigences de capital réglementaire de la banque. L'inclusion de CWB pourrait modifier la pondération des actifs en fonction des risques, influençant ainsi les ratios de capital réglementaire. Cela est crucial pour la conformité aux attentes prudentielles et pour la comparabilité entre pairs. Point de surveillance : Surveiller l'impact de l'inclusion de CWB sur les ratios de capital et s'assurer que la banque reste conforme aux exigences réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : BNC modifie le tableau des actions et autres instruments de capitaux propres en ajoutant les indicateurs Série 47 et Série 49, tout en supprimant l'indicateur Série 32. Pertinence métier : Ce changement met en évidence une réorganisation des instruments de capitaux propres de la BNC, ce qui peut affecter la composition des fonds propres réglementaires. L'ajout des Séries 47 et 49 pourrait indiquer l'émission de nouveaux instruments de capital, tandis que la suppression de la Série 32 pourrait signaler le rachat ou l'échéance d'un instrument existant. Cela a un impact direct sur la structure du capital réglementaire et la capacité de la banque à répondre aux exigences de fonds propres. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la conformité aux exigences prudentielles.</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1708,17 +1696,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1728,18 +1716,18 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Émission d'actions ordinaires relatives à l'acquisition de CWB</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Série 32</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Structure du rapport Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025. Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres. Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : BNC modifie le tableau des actions et autres instruments de capitaux propres en ajoutant les indicateurs Série 47 et Série 49, tout en supprimant l'indicateur Série 32. Pertinence métier : Ce changement met en évidence une réorganisation des instruments de capitaux propres de la BNC, ce qui peut affecter la composition des fonds propres réglementaires. L'ajout des Séries 47 et 49 pourrait indiquer l'émission de nouveaux instruments de capital, tandis que la suppression de la Série 32 pourrait signaler le rachat ou l'échéance d'un instrument existant. Cela a un impact direct sur la structure du capital réglementaire et la capacité de la banque à répondre aux exigences de fonds propres. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la conformité aux exigences prudentielles.</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1759,22 +1747,22 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
+          <t>Capital réglementaire (1), ratio de levier (1) et TLAC (2)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1785,12 +1773,12 @@
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Options de remplacement relatives à l'acquisition de CWB</t>
+          <t>Les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Structure du rapport Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025. Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres. Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Ratio ou seuil prudentiel Ce qui change : BNC modifie le tableau du capital réglementaire pour inclure des notes sur le rachat des BCRL - Série 1 effectué le 17 novembre 2025. Pertinence métier : Ce changement met en évidence l'impact du rachat des BCRL - Série 1 sur les ratios de capital réglementaire de la BNC. En intégrant ces données, la banque améliore la transparence de ses divulgations financières et permet une meilleure évaluation de sa position en capital par rapport aux exigences réglementaires. Cela pourrait également influencer la perception des investisseurs et des régulateurs sur la solidité financière de la banque. Point de surveillance : Surveiller l'impact de ce rachat sur les ratios de capital et de levier, ainsi que sur la conformité aux exigences TLAC.</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1810,17 +1798,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
+          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1830,22 +1818,18 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Les données de 2023 n’ont pas été ajustées pour tenir compte des modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
+          <t>Les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Structure du rapport Ce qui change : Ajout des indicateurs 'Émission d'actions ordinaires relatives à l'acquisition de CWB' et 'Options de remplacement relatives à l'acquisition de CWB' dans le tableau de variation des fonds propres réglementaires. Modification de la note pour inclure le rachat des BCRL - Série 1 au 31 octobre 2025. Pertinence métier : Ce changement met l'accent sur l'impact des acquisitions sur les fonds propres réglementaires de la banque. L'ajout de ces indicateurs reflète une stratégie d'expansion par acquisition, ce qui peut influencer la structure du capital et les exigences réglementaires associées. La modification de la note indique une mise à jour importante concernant le rachat d'instruments de capital, ce qui est crucial pour la gestion des fonds propres. Point de surveillance : Surveiller l'impact de l'acquisition de CWB sur les fonds propres réglementaires et la conformité aux exigences de capital, ainsi que les implications du rachat des BCRL - Série 1.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Ratio ou seuil prudentiel, Capital réglementaire Ce qui change : BNC modifie les notes du tableau des exigences réglementaires pour inclure l'impact du rachat des BCRL - Série 1 et met à jour la date de confirmation de la réserve pour stabilité intérieure par le BSIF. Pertinence métier : Ce changement met en évidence l'impact des événements récents sur les ratios réglementaires de la BNC, notamment le rachat des BCRL - Série 1. La mise à jour de la date de confirmation par le BSIF reflète une évolution dans la gestion des réserves de stabilité intérieure, ce qui peut influencer la perception de la solidité financière de la banque. Cela améliore la transparence et l'alignement avec les exigences réglementaires actuelles, tout en permettant une meilleure comparabilité avec les pairs. Point de surveillance : Surveiller l'impact du rachat sur les ratios de fonds propres et la conformité continue avec les exigences du BSIF.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1858,161 +1842,161 @@
       <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Variation des fonds propres réglementaires (1)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Émission d'actions ordinaires relatives à l'acquisition de CWB</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : BNC ajoute des indicateurs liés à l'émission d'actions ordinaires et aux options de remplacement dans le cadre de l'acquisition de CWB, et modifie les notes pour inclure le rachat des BCRL - Série 1. Pertinence métier : Ce changement met en évidence l'impact de l'acquisition de CWB sur les fonds propres réglementaires de la BNC. L'ajout d'indicateurs spécifiques à cette acquisition souligne l'importance de cette transaction pour la structure du capital de la banque. Cela affecte la transparence et la comparabilité des fonds propres réglementaires, car il est crucial de comprendre comment les acquisitions influencent les ratios de capital et la capacité de la banque à respecter les exigences réglementaires. Point de surveillance : Surveiller l'évolution des fonds propres réglementaires de la BNC suite à l'acquisition de CWB et l'impact sur les ratios de capital.</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Variation des fonds propres réglementaires (1)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Indicateur</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Options de remplacement relatives à l'acquisition de CWB</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : BNC ajoute des indicateurs liés à l'émission d'actions ordinaires et aux options de remplacement dans le cadre de l'acquisition de CWB, et modifie les notes pour inclure le rachat des BCRL - Série 1. Pertinence métier : Ce changement met en évidence l'impact de l'acquisition de CWB sur les fonds propres réglementaires de la BNC. L'ajout d'indicateurs spécifiques à cette acquisition souligne l'importance de cette transaction pour la structure du capital de la banque. Cela affecte la transparence et la comparabilité des fonds propres réglementaires, car il est crucial de comprendre comment les acquisitions influencent les ratios de capital et la capacité de la banque à respecter les exigences réglementaires. Point de surveillance : Surveiller l'évolution des fonds propres réglementaires de la BNC suite à l'acquisition de CWB et l'impact sur les ratios de capital.</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Variation des fonds propres réglementaires (1)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Pour de plus amples renseignements, se reporter aux notes 17 et 18 afférentes aux états financiers consolidés.</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Modification</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Pour de plus amples renseignements, se reporter aux notes 18 et 19 afférentes aux états financiers consolidés.</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Pour de plus amples renseignements, se reporter à la note 23 afférente aux états financiers consolidés.</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr"/>
-      <c r="L28" s="4" t="inlineStr"/>
-      <c r="M28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Pour de plus amples renseignements, se reporter à la note 25 afférente aux états financiers consolidés.</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Méthode de calcul ou approche modifiée Ce qui change : L'indicateur 'Acceptations' a été supprimé et 'Prêts et acceptations, déduction faite des provisions' a été renommé en 'Prêts, déduction faite des provisions'. De plus, des notes ont été ajoutées et supprimées, modifiant la référence aux états financiers consolidés. Pertinence métier : Ce changement met l'accent sur une réorganisation des indicateurs de risque dans la section de gestion des risques, ce qui peut refléter une modification dans la manière dont la banque évalue ou présente ses expositions. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent indiquer un changement dans la méthodologie de calcul ou de présentation des risques, ce qui est crucial pour la comparabilité entre pairs et la conformité aux attentes réglementaires. Point de surveillance : Surveiller l'impact de ces changements sur la présentation des risques et la conformité aux normes comptables et réglementaires.</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr"/>
-      <c r="M29" s="4" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Les données de 2023 n’ont pas été ajustées pour tenir compte des modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : BNC ajoute des indicateurs liés à l'émission d'actions ordinaires et aux options de remplacement dans le cadre de l'acquisition de CWB, et modifie les notes pour inclure le rachat des BCRL - Série 1. Pertinence métier : Ce changement met en évidence l'impact de l'acquisition de CWB sur les fonds propres réglementaires de la BNC. L'ajout d'indicateurs spécifiques à cette acquisition souligne l'importance de cette transaction pour la structure du capital de la banque. Cela affecte la transparence et la comparabilité des fonds propres réglementaires, car il est crucial de comprendre comment les acquisitions influencent les ratios de capital et la capacité de la banque à respecter les exigences réglementaires. Point de surveillance : Surveiller l'évolution des fonds propres réglementaires de la BNC suite à l'acquisition de CWB et l'impact sur les ratios de capital.</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2022,17 +2006,17 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
+          <t>(sans titre)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2048,12 +2032,12 @@
       <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Incluent les billets de dépôt au porteur.</t>
+          <t>Pour de plus amples renseignements, se reporter aux notes 17 et 18 afférentes aux états financiers consolidés.</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2073,17 +2057,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
+          <t>(sans titre)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2093,18 +2077,22 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Les acceptations bancaires ne sont pas incluses dans ce tableau.</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr"/>
+          <t>Pour de plus amples renseignements, se reporter aux notes 18 et 19 afférentes aux états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter à la note 23 afférente aux états financiers consolidés.</t>
+        </is>
+      </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : L'indicateur 'Titrisation de créances sur cartes de crédit' a été supprimé du tableau des échéances contractuelles résiduelles du financement institutionnel. De plus, plusieurs notes ont été ajoutées, supprimées ou modifiées, notamment l'ajout de la note 'Incluent les billets de dépôt au porteur.' et la modification de la note sur les dettes faisant l'objet de règlements de conversion. Pertinence métier : Ce changement met en évidence une révision de la manière dont la banque présente ses échéances contractuelles, ce qui pourrait affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur de titrisation et les modifications des notes peuvent indiquer un changement dans la gestion des risques liés au financement institutionnel. Point de surveillance : Surveiller l'impact de ces modifications sur la divulgation des risques financiers et la conformité aux attentes réglementaires en matière de transparence et de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2119,47 +2107,47 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Gestion du capital</t>
+          <t>Gestion des risques</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
+          <t>(sans titre)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Renommage</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Le 18 juin 2024, le BSIF a confirmé que la réserve pour stabilité intérieure était maintenue à 3,5 %.</t>
+          <t>Prêts et acceptations, déduction faite des provisions</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Le 26 juin 2025, le BSIF a confirmé que la réserve pour stabilité intérieure était maintenue à 3,5%.</t>
+          <t>Prêts, déduction faite des provisions</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Exigences réglementaires ou conformité, Ratio ou seuil prudentiel Ce qui change : La note modifiée indique un changement de date concernant la confirmation par le BSIF de la réserve pour stabilité intérieure, passant du 18 juin 2024 au 26 juin 2025. De plus, une nouvelle note mentionne que les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025. Pertinence métier : Ce changement met en évidence une mise à jour des exigences réglementaires et des ratios prudentiels, ce qui est crucial pour la conformité et la gestion des fonds propres de la banque. La modification de la date de confirmation par le BSIF peut indiquer un ajustement dans les attentes réglementaires, tandis que la prise en compte du rachat des BCRL dans les ratios souligne l'impact des décisions de financement sur les exigences de capital. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de fonds propres et la conformité aux exigences du BSIF, ainsi que l'effet du rachat des BCRL sur la structure de capital.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée Ce qui change : BNC modifie les indicateurs en supprimant les participations dans des entreprises associées et des coentreprises, et en renommant les prêts et acceptations, déduction faite des provisions, en prêts, déduction faite des provisions. De plus, certaines notes ont été supprimées en raison de modifications de méthodes comptables liées à l'adoption de l'IFRS 17. Pertinence métier : Ce changement met en évidence une révision des méthodes comptables et des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières de la BNC. L'adoption de l'IFRS 17 pourrait avoir des implications sur la manière dont les actifs et passifs sont évalués, influençant ainsi la perception des risques financiers et la gestion des fonds propres. Cela pourrait également impacter la manière dont la BNC communique ses risques aux investisseurs et aux régulateurs. Point de surveillance : Surveiller l'impact de l'adoption de l'IFRS 17 sur les rapports financiers et la gestion des risques de la BNC.</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2182,27 +2170,35 @@
           <t>(sans titre)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr"/>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter à la note 25 afférente aux états financiers consolidés.</t>
+        </is>
+      </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Information ajoutée, Gouvernance des risques Ce qui change : Un nouveau tableau a été ajouté dans la section gestion des risques, listant divers types de risques, y compris le risque de non-conformité à la réglementation et le risque environnemental et social. Pertinence métier : Ce changement met l'accent sur une approche plus holistique de la gestion des risques en incluant une gamme étendue de risques, tels que le risque environnemental et social, qui sont de plus en plus pertinents dans le contexte actuel de réglementation accrue et de préoccupations ESG. Cela reflète une volonté de la banque de renforcer sa gouvernance des risques en intégrant des facteurs de risque plus diversifiés. Point de surveillance : Surveiller comment cette nouvelle divulgation influence la stratégie de gestion des risques de la banque et si elle entraîne des ajustements dans les processus de gouvernance des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2222,30 +2218,38 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Ajout</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Incluent les billets de dépôt au porteur.</t>
+        </is>
+      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Information retirée, Risque émergent : cybersécurité Ce qui change : Le tableau concernant les indicateurs de sécurité de l'information a été supprimé dans le rapport courant. Pertinence métier : Ce changement met en évidence une potentielle réduction de la transparence sur la gestion des risques liés à la cybersécurité. La sécurité de l'information est un domaine critique, surtout avec l'augmentation des cyberattaques. La suppression de ce tableau pourrait indiquer un changement de posture ou une réévaluation de la manière dont ces informations sont communiquées aux parties prenantes. Point de surveillance : Il est crucial de surveiller si cette suppression est compensée par d'autres formes de divulgation ou si elle reflète un changement dans la gestion des risques de cybersécurité.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2265,30 +2269,42 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr"/>
+          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Le 18 juin 2024, le BSIF a confirmé que la réserve pour stabilité intérieure était maintenue à 3,5 %.</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Le 26 juin 2025, le BSIF a confirmé que la réserve pour stabilité intérieure était maintenue à 3,5%.</t>
+        </is>
+      </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Information ajoutée Ce qui change : Un nouveau tableau a été ajouté dans la section gestion du capital, présentant des indicateurs pour le crédit, le marché, l'opérationnel, et d'autres risques, ainsi qu'un total. Pertinence métier : Ce changement met en évidence une nouvelle approche de la banque pour divulguer des informations sur la gestion du capital. L'ajout de ce tableau pourrait indiquer une volonté de transparence accrue ou une réponse à des attentes réglementaires spécifiques concernant la gestion des risques et du capital. Cela permet une meilleure comparabilité entre pairs et peut refléter une adaptation aux exigences prudentielles. Point de surveillance : Surveiller si ce tableau est lié à de nouvelles exigences réglementaires ou à une modification de la stratégie de gestion du capital de la banque.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Ratio ou seuil prudentiel, Capital réglementaire Ce qui change : BNC modifie les notes du tableau des exigences réglementaires pour inclure l'impact du rachat des BCRL - Série 1 et met à jour la date de confirmation de la réserve pour stabilité intérieure par le BSIF. Pertinence métier : Ce changement met en évidence l'impact des événements récents sur les ratios réglementaires de la BNC, notamment le rachat des BCRL - Série 1. La mise à jour de la date de confirmation par le BSIF reflète une évolution dans la gestion des réserves de stabilité intérieure, ce qui peut influencer la perception de la solidité financière de la banque. Cela améliore la transparence et l'alignement avec les exigences réglementaires actuelles, tout en permettant une meilleure comparabilité avec les pairs. Point de surveillance : Surveiller l'impact du rachat sur les ratios de fonds propres et la conformité continue avec les exigences du BSIF.</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2331,7 +2347,7 @@
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : Un nouveau tableau a été ajouté dans la section capital_management, présentant des indicateurs pour le Crédit, le Marché, l'Opérationnel et le Total. Pertinence métier : Ce changement met l'accent sur la transparence accrue dans la gestion du capital de la banque. L'ajout de ce tableau permet une meilleure compréhension des composantes du capital réglementaire, ce qui est crucial pour la conformité aux exigences prudentielles et pour la comparabilité entre pairs. Point de surveillance : Surveiller l'impact de ce nouveau tableau sur la divulgation des ratios de capital et s'assurer qu'il est aligné avec les attentes réglementaires en matière de transparence et de gestion du capital.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Gouvernance des risques Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs de risque pour le crédit, le marché, l'opérationnel et d'autres risques. Pertinence métier : Ce changement met en évidence une amélioration de la transparence et de la gouvernance des risques de la BNC. L'ajout de ce tableau permet une meilleure compréhension des différents types de risques auxquels la banque est exposée, ce qui est crucial pour les actionnaires et les régulateurs. Cela renforce la capacité de la banque à communiquer efficacement sur sa gestion des risques et à se comparer à ses pairs en termes de divulgation de risques. Point de surveillance : Surveiller l'impact de ce tableau sur la perception des risques par les investisseurs et les régulateurs, ainsi que sur la stratégie de gestion des risques de la BNC.</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2374,7 +2390,7 @@
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : Un nouveau tableau a été ajouté dans la section gestion du capital, présentant des indicateurs pour le crédit, le marché, l'opérationnel et le total. Pertinence métier : Ce changement met en évidence une nouvelle approche de la banque pour divulguer des informations sur ses indicateurs de capital. Cela pourrait refléter une réponse aux attentes réglementaires accrues en matière de transparence et de gestion des risques. La présentation de ces indicateurs est cruciale pour évaluer la santé financière de la banque et sa conformité aux exigences de capital réglementaire. Point de surveillance : Surveiller comment ces indicateurs influencent la gestion du capital et la conformité réglementaire de la banque, ainsi que toute mise à jour future de la méthodologie de calcul ou de présentation.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs liés aux risques de crédit, de marché et opérationnel, ainsi que le total. Pertinence métier : Ce changement met en évidence une amélioration de la transparence dans la divulgation des risques financiers et de leur impact sur le capital réglementaire de la banque. En ajoutant ce tableau, BNC fournit une vue plus détaillée et structurée des composantes de risque qui influencent ses exigences en capital, ce qui est crucial pour les investisseurs et les régulateurs. Cela permet également une meilleure comparabilité avec les pairs et une évaluation plus précise de la résilience de la banque face aux chocs financiers. Point de surveillance : Surveiller l'impact de cette nouvelle divulgation sur la perception des risques par les parties prenantes et son alignement avec les exigences réglementaires.</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2417,7 +2433,7 @@
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : Un nouveau tableau a été ajouté dans la section capital_management, présentant des indicateurs pour le Crédit, le Marché, l'Opérationnel et le Total. Pertinence métier : Ce changement met l'accent sur la transparence accrue dans la gestion du capital de la banque. L'ajout de ce tableau permet une meilleure compréhension des composantes du capital réglementaire, ce qui est crucial pour les attentes prudentielles et la comparabilité entre pairs. Cela pourrait également indiquer une réponse aux exigences réglementaires croissantes en matière de divulgation. Point de surveillance : Surveiller l'impact de cette nouvelle divulgation sur la perception des investisseurs et des régulateurs, ainsi que son alignement avec les attentes réglementaires en matière de capital.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs liés aux risques de crédit, de marché et opérationnel. Pertinence métier : Ce changement met en évidence une amélioration de la transparence dans la divulgation des risques financiers de la BNC. En ajoutant un tableau spécifique aux indicateurs de risque, la banque fournit une vue plus détaillée et structurée de son exposition aux risques de crédit, de marché et opérationnel. Cela renforce la capacité des parties prenantes à évaluer la résilience de la banque face aux chocs financiers et à comparer sa gestion des risques avec celle de ses pairs. Point de surveillance : Surveiller l'impact de cette nouvelle divulgation sur la compréhension des risques financiers par les investisseurs et les régulateurs.</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2429,8 +2445,51 @@
       <c r="L38" s="4" t="inlineStr"/>
       <c r="M38" s="4" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs liés aux risques de crédit, de marché et opérationnel, ainsi que le total. Pertinence métier : Ce changement met en évidence une nouvelle approche de la BNC pour la divulgation de ses risques financiers, en intégrant un tableau qui synthétise les indicateurs clés de risque. Cela améliore la transparence et la comparabilité des informations sur le capital réglementaire, ce qui est crucial pour les investisseurs et les régulateurs. En fournissant une vue consolidée des risques, la BNC renforce sa capacité à démontrer sa résilience face aux chocs financiers potentiels. Point de surveillance : Surveiller l'impact de ce tableau sur la compréhension des risques financiers et la conformité aux exigences réglementaires.</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M38"/>
+  <autoFilter ref="A1:M39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
+++ b/outputs/resultats/bnc/2025_t4_vs_2024_t4/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -550,17 +550,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Exigences de déclaration relatives au ratio de liquidité à long terme (1) (2) *</t>
+          <t>(sans titre)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,27 +570,23 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>(3) Les valeurs pondérées sont calculées après l’application des pondérations prescrites par la ligne directrice NI du BSIF.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>(3) Les valeurs pondérées sont calculées après l’application des pondérations prescrites par la ligne directrice NL du BSIF.</t>
-        </is>
-      </c>
+          <t>Certains montants ont été ajustés à la suite de modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Texte de risque modifié Ce qui change : BNC modifie une note de bas de tableau sans changement substantiel de contenu. Pertinence métier : Ce changement est purement cosmétique et n'affecte pas la substance de la divulgation. Il s'agit d'une reformulation sans impact sur la compréhension ou la gestion des risques de liquidité. Aucune nouvelle information n'est introduite, et la modification n'a pas d'incidence sur la transparence ou la comparabilité des pratiques de gestion des risques de la banque. Point de surveillance : Aucun point de surveillance particulier n'est requis pour cette modification cosmétique.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Structure du rapport Ce qui change : BNC modifie le tableau de gestion des risques en supprimant les indicateurs liés aux participations dans des entreprises associées et des coentreprises, et ajuste certains montants suite à l'adoption de l'IFRS 17. Pertinence métier : Ce changement met en évidence une modification de la méthodologie comptable de la BNC, ce qui peut affecter la transparence et la comparabilité des informations financières. L'adoption de l'IFRS 17 implique des ajustements significatifs dans la présentation des états financiers, ce qui peut avoir un impact sur la perception des risques associés aux participations. Cela souligne également l'importance de la conformité aux nouvelles normes comptables internationales, ce qui est crucial pour maintenir la confiance des investisseurs et des régulateurs. Point de surveillance : Surveiller l'impact de l'adoption de l'IFRS 17 sur la présentation des risques et la comparabilité des états financiers de la BNC.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -640,7 +636,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur 'Titrisation de créances sur cartes de crédit' et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la présentation des échéances de financement, ce qui peut affecter la transparence et la compréhension des engagements financiers de la banque. La suppression de l'indicateur de titrisation de créances sur cartes de crédit pourrait indiquer un changement dans la stratégie de financement ou de gestion des risques de liquidité. Les modifications des notes, notamment l'inclusion des dettes sujettes à des règlements de conversion, soulignent une attention accrue aux exigences de recapitalisation interne, ce qui est crucial pour la résilience financière. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion de la liquidité et la conformité aux exigences réglementaires de recapitalisation interne.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -691,7 +687,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur 'Titrisation de créances sur cartes de crédit' et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la présentation des échéances de financement, ce qui peut affecter la transparence et la compréhension des engagements financiers de la banque. La suppression de l'indicateur de titrisation de créances sur cartes de crédit pourrait indiquer un changement dans la stratégie de financement ou de gestion des risques de liquidité. Les modifications des notes, notamment l'inclusion des dettes sujettes à des règlements de conversion, soulignent une attention accrue aux exigences de recapitalisation interne, ce qui est crucial pour la résilience financière. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion de la liquidité et la conformité aux exigences réglementaires de recapitalisation interne.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -746,7 +742,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Texte de risque modifié Ce qui change : BNC modifie une note de bas de tableau en changeant le temps verbal de 'est en cours de va' à 'a récemment été ap'. Pertinence métier : Ce changement est purement cosmétique et n'affecte pas la substance de la divulgation. Il s'agit d'une simple correction de formulation qui ne modifie ni les risques, ni la gouvernance, ni les exigences réglementaires. La modification n'introduit pas de nouvelle information ni ne change la posture de la banque en matière de gestion des risques. Point de surveillance : Aucun point de surveillance particulier n'est requis pour ce changement, car il n'affecte pas la gestion des risques ou la conformité réglementaire.</t>
+          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Texte de risque modifié Ce qui change : BNC modifie une note de bas de tableau en changeant le temps verbal de 'est en cours de va' à 'a récemment été ap'. Pertinence métier : Ce changement est purement cosmétique et n'affecte pas la substance de la divulgation. Il s'agit d'une simple correction de formulation qui n'introduit ni ne retire aucune information nouvelle ou substantielle concernant la gestion des risques ou les exigences réglementaires. La modification n'a pas d'impact sur la transparence ou la comparabilité des pratiques de gestion des risques de la banque. Point de surveillance : Aucun point de surveillance particulier n'est requis pour ce changement, car il ne modifie pas la posture de gestion des risques de la banque.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -801,7 +797,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : BNC modifie le tableau de gestion des risques en supprimant l'indicateur 'Acceptations' et en renommant 'Prêts et acceptations, déduction faite des provisions' en 'Prêts, déduction faite des provisions'. Pertinence métier : Ce changement met en évidence une révision de la présentation des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent modifier la perception des risques de crédit et la manière dont la banque communique ses expositions. Cela pourrait également influencer la compréhension des risques par les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la communication des risques de crédit et la clarté des informations financières fournies par la BNC.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -841,18 +837,22 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Renommage</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Acceptations</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
+          <t>Prêts et acceptations, déduction faite des provisions</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Prêts, déduction faite des provisions</t>
+        </is>
+      </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : BNC modifie le tableau de gestion des risques en supprimant l'indicateur 'Acceptations' et en renommant 'Prêts et acceptations, déduction faite des provisions' en 'Prêts, déduction faite des provisions'. Pertinence métier : Ce changement met en évidence une révision de la présentation des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent modifier la perception des risques de crédit et la manière dont la banque communique ses expositions. Cela pourrait également influencer la compréhension des risques par les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la communication des risques de crédit et la clarté des informations financières fournies par la BNC.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -861,16 +861,8 @@
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-30T22:24:17.096512+00:00</t>
-        </is>
-      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -895,7 +887,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -905,13 +897,13 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Positions liées aux activités de négociation pour lesquelles la mesure du risque est la VaR totale. Pour de plus amples renseignements, se reporter au tableau illustrant la distribution de la VaR des portefeuilles de négociation par catégorie de risque et leur effet de diversification présenté à la page suivante.</t>
+          <t>Acceptations</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : BNC modifie le tableau de gestion des risques en supprimant l'indicateur 'Acceptations' et en renommant 'Prêts et acceptations, déduction faite des provisions' en 'Prêts, déduction faite des provisions'. Pertinence métier : Ce changement met en évidence une révision de la présentation des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent modifier la perception des risques de crédit et la manière dont la banque communique ses expositions. Cela pourrait également influencer la compréhension des risques par les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la communication des risques de crédit et la clarté des informations financières fournies par la BNC.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -936,17 +928,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -956,13 +948,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Participations dans des entreprises associées et des coentreprises</t>
+          <t>Positions liées aux activités de négociation pour lesquelles la mesure du risque est la VaR totale. Pour de plus amples renseignements, se reporter au tableau illustrant la distribution de la VaR des portefeuilles de négociation par catégorie de risque et leur effet de diversification présenté à la page suivante.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée Ce qui change : BNC modifie les indicateurs en supprimant les participations dans des entreprises associées et des coentreprises, et en renommant les prêts et acceptations, déduction faite des provisions, en prêts, déduction faite des provisions. De plus, certaines notes ont été supprimées en raison de modifications de méthodes comptables liées à l'adoption de l'IFRS 17. Pertinence métier : Ce changement met en évidence une révision des méthodes comptables et des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières de la BNC. L'adoption de l'IFRS 17 pourrait avoir des implications sur la manière dont les actifs et passifs sont évalués, influençant ainsi la perception des risques financiers et la gestion des fonds propres. Cela pourrait également impacter la manière dont la BNC communique ses risques aux investisseurs et aux régulateurs. Point de surveillance : Surveiller l'impact de l'adoption de l'IFRS 17 sur les rapports financiers et la gestion des risques de la BNC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : BNC modifie le tableau de gestion des risques en supprimant l'indicateur 'Acceptations' et en renommant 'Prêts et acceptations, déduction faite des provisions' en 'Prêts, déduction faite des provisions'. Pertinence métier : Ce changement met en évidence une révision de la présentation des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent modifier la perception des risques de crédit et la manière dont la banque communique ses expositions. Cela pourrait également influencer la compréhension des risques par les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la communication des risques de crédit et la clarté des informations financières fournies par la BNC.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -997,7 +989,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1007,13 +999,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Certains montants ont été ajustés à la suite de modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
+          <t>Participations dans des entreprises associées et des coentreprises</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée Ce qui change : BNC modifie les indicateurs en supprimant les participations dans des entreprises associées et des coentreprises, et en renommant les prêts et acceptations, déduction faite des provisions, en prêts, déduction faite des provisions. De plus, certaines notes ont été supprimées en raison de modifications de méthodes comptables liées à l'adoption de l'IFRS 17. Pertinence métier : Ce changement met en évidence une révision des méthodes comptables et des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières de la BNC. L'adoption de l'IFRS 17 pourrait avoir des implications sur la manière dont les actifs et passifs sont évalués, influençant ainsi la perception des risques financiers et la gestion des fonds propres. Cela pourrait également impacter la manière dont la BNC communique ses risques aux investisseurs et aux régulateurs. Point de surveillance : Surveiller l'impact de l'adoption de l'IFRS 17 sur les rapports financiers et la gestion des risques de la BNC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée, Structure du rapport Ce qui change : BNC modifie le tableau de gestion des risques en supprimant les indicateurs liés aux participations dans des entreprises associées et des coentreprises, et ajuste certains montants suite à l'adoption de l'IFRS 17. Pertinence métier : Ce changement met en évidence une modification de la méthodologie comptable de la BNC, ce qui peut affecter la transparence et la comparabilité des informations financières. L'adoption de l'IFRS 17 implique des ajustements significatifs dans la présentation des états financiers, ce qui peut avoir un impact sur la perception des risques associés aux participations. Cela souligne également l'importance de la conformité aux nouvelles normes comptables internationales, ce qui est crucial pour maintenir la confiance des investisseurs et des régulateurs. Point de surveillance : Surveiller l'impact de l'adoption de l'IFRS 17 sur la présentation des risques et la comparabilité des états financiers de la BNC.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1033,43 +1025,47 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Exposition maximale au risque de crédit selon les catégories d’actifs de Bâle (1) *</t>
+          <t>Conciliation du risque de marché avec les éléments du bilan consolidé *</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Particuliers – Total</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
+          <t>Pour de plus amples renseignements, se reporter aux notes 18 et 19 afférentes aux états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter aux notes 17 et 18 afférentes aux états financiers consolidés.</t>
+        </is>
+      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Ratio ou seuil prudentiel Ce qui change : BNC supprime plusieurs indicateurs clés du tableau d'exposition maximale au risque de crédit, notamment les totaux pour les catégories Particuliers, Autres que particuliers, Portefeuille de négociation et Titrisation. Pertinence métier : Ce changement met en évidence une modification substantielle dans la manière dont la BNC présente son exposition au risque de crédit. La suppression de ces indicateurs pourrait affecter la transparence et la comparabilité des risques de crédit de la banque par rapport à ses pairs, en particulier en ce qui concerne les ratios réglementaires et les exigences de Bâle. Cela pourrait également influencer la perception des investisseurs et des régulateurs sur la gestion des risques de crédit de la banque. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des divulgations de risque de crédit et la conformité aux exigences réglementaires.</t>
+          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Références de notes modifiées Ce qui change : BNC modifie les références de notes dans le tableau de conciliation du risque de marché avec les éléments du bilan consolidé, passant de 18 et 19 à 17 et 18, et de 25 à 23. Pertinence métier : Ce changement concerne uniquement la mise à jour des références de notes dans le tableau, ce qui n'affecte pas la substance des divulgations de risque de marché. Il s'agit d'une correction de numérotation qui n'a pas d'impact sur la gestion des risques ou la conformité réglementaire. Par conséquent, cela ne constitue pas une nouvelle idée substantielle. Point de surveillance : Aucun point de surveillance particulier n'est requis pour ce changement de numérotation des notes.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
@@ -1084,43 +1080,47 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Exposition maximale au risque de crédit selon les catégories d’actifs de Bâle (1) *</t>
+          <t>Conciliation du risque de marché avec les éléments du bilan consolidé *</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Autres que particuliers – Total</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
+          <t>Pour de plus amples renseignements, se reporter à la note 25 afférente aux états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter à la note 23 afférente aux états financiers consolidés.</t>
+        </is>
+      </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Ratio ou seuil prudentiel Ce qui change : BNC supprime plusieurs indicateurs clés du tableau d'exposition maximale au risque de crédit, notamment les totaux pour les catégories Particuliers, Autres que particuliers, Portefeuille de négociation et Titrisation. Pertinence métier : Ce changement met en évidence une modification substantielle dans la manière dont la BNC présente son exposition au risque de crédit. La suppression de ces indicateurs pourrait affecter la transparence et la comparabilité des risques de crédit de la banque par rapport à ses pairs, en particulier en ce qui concerne les ratios réglementaires et les exigences de Bâle. Cela pourrait également influencer la perception des investisseurs et des régulateurs sur la gestion des risques de crédit de la banque. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des divulgations de risque de crédit et la conformité aux exigences réglementaires.</t>
+          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Références de notes modifiées Ce qui change : BNC modifie les références de notes dans le tableau de conciliation du risque de marché avec les éléments du bilan consolidé, passant de 18 et 19 à 17 et 18, et de 25 à 23. Pertinence métier : Ce changement concerne uniquement la mise à jour des références de notes dans le tableau, ce qui n'affecte pas la substance des divulgations de risque de marché. Il s'agit d'une correction de numérotation qui n'a pas d'impact sur la gestion des risques ou la conformité réglementaire. Par conséquent, cela ne constitue pas une nouvelle idée substantielle. Point de surveillance : Aucun point de surveillance particulier n'est requis pour ce changement de numérotation des notes.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
@@ -1135,43 +1135,47 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Exposition maximale au risque de crédit selon les catégories d’actifs de Bâle (1) *</t>
+          <t>Exigences de déclaration relatives au ratio de liquidité à long terme (1) (2) *</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Portefeuille de négociation – Total</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
+          <t>(3) Les valeurs pondérées sont calculées après l’application des pondérations prescrites par la ligne directrice NI du BSIF.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>(3) Les valeurs pondérées sont calculées après l’application des pondérations prescrites par la ligne directrice NL du BSIF.</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Ratio ou seuil prudentiel Ce qui change : BNC supprime plusieurs indicateurs clés du tableau d'exposition maximale au risque de crédit, notamment les totaux pour les catégories Particuliers, Autres que particuliers, Portefeuille de négociation et Titrisation. Pertinence métier : Ce changement met en évidence une modification substantielle dans la manière dont la BNC présente son exposition au risque de crédit. La suppression de ces indicateurs pourrait affecter la transparence et la comparabilité des risques de crédit de la banque par rapport à ses pairs, en particulier en ce qui concerne les ratios réglementaires et les exigences de Bâle. Cela pourrait également influencer la perception des investisseurs et des régulateurs sur la gestion des risques de crédit de la banque. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des divulgations de risque de crédit et la conformité aux exigences réglementaires.</t>
+          <t>NON — Nouvel élément à surveiller : Non Sujet détecté : Texte de risque modifié Ce qui change : BNC modifie une note de bas de tableau sans changement substantiel du contenu. Pertinence métier : Ce changement est purement cosmétique et n'affecte pas la substance de la divulgation. Il s'agit d'une reformulation sans impact sur la compréhension ou la gestion des risques de liquidité. Aucune nouvelle information n'est introduite, et la modification n'a pas d'incidence sur la transparence ou la comparabilité des pratiques de gestion des risques de la banque. Point de surveillance : Aucun point de surveillance requis, car le changement n'affecte pas la divulgation des risques ou la conformité réglementaire.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
@@ -1186,38 +1190,38 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Exposition maximale au risque de crédit selon les catégories d’actifs de Bâle (1) *</t>
+          <t>Notations de crédit de la Banque</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Titrisation – Total</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Le 17 octobre 2025, S&amp;P Global Ratings (S&amp;P) a révisé à la hausse la notation de la dette à long terme de premier rang non assujettie au régime de recapitalisation interne des banques, la dette à long terme de premier rang, la dette subordonnée FPUNV, les billets de capital à recours limité FPUNV et les actions privilégiées FPUNV de la Banque.</t>
+        </is>
+      </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Ratio ou seuil prudentiel Ce qui change : BNC supprime plusieurs indicateurs clés du tableau d'exposition maximale au risque de crédit, notamment les totaux pour les catégories Particuliers, Autres que particuliers, Portefeuille de négociation et Titrisation. Pertinence métier : Ce changement met en évidence une modification substantielle dans la manière dont la BNC présente son exposition au risque de crédit. La suppression de ces indicateurs pourrait affecter la transparence et la comparabilité des risques de crédit de la banque par rapport à ses pairs, en particulier en ce qui concerne les ratios réglementaires et les exigences de Bâle. Cela pourrait également influencer la perception des investisseurs et des régulateurs sur la gestion des risques de crédit de la banque. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des divulgations de risque de crédit et la conformité aux exigences réglementaires.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Facteur de risque modifié Ce qui change : BNC modifie les notations de crédit en intégrant une révision à la hausse par S&amp;P Global Ratings et en supprimant une révision par Moody's. Pertinence métier : Ce changement met en évidence une amélioration de la perception du risque de crédit de la BNC par les agences de notation, ce qui peut influencer positivement la confiance des investisseurs et réduire les coûts de financement. La révision à la hausse par S&amp;P indique une amélioration de la qualité de crédit perçue, tandis que la suppression de la révision par Moody's pourrait signaler une stabilisation des notations. Cela affecte la transparence et la gestion des risques de crédit de la banque, en alignant ses notations sur les attentes du marché. Point de surveillance : Surveiller l'impact de ces changements de notation sur les conditions de financement et la perception du risque de crédit par d'autres parties prenantes.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1257,18 +1261,18 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Le 17 octobre 2025, S&amp;P Global Ratings (S&amp;P) a révisé à la hausse la notation de la dette à long terme de premier rang non assujettie au régime de recapitalisation interne des banques, la dette à long terme de premier rang, la dette subordonnée FPUNV, les billets de capital à recours limité FPUNV et les actions privilégiées FPUNV de la Banque.</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Le 24 septembre 2024, Moody's a placé sous révision en vue d’une révision à la hausse toutes les notations et évaluations à long terme de la Banque, y compris son évaluation de crédit de base Baa1, les notations de dépôts à long terme Aa3 et les notations de risque de contrepartie, ainsi que son évaluation de risque de contrepartie de Aa3(cr).</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Facteur de risque modifié Ce qui change : BNC modifie les notations de crédit en intégrant une révision à la hausse par S&amp;P Global Ratings et en supprimant une révision par Moody's. Pertinence métier : Ce changement met en évidence une amélioration de la perception du risque de crédit de la BNC par S&amp;P, ce qui peut influencer positivement la confiance des investisseurs et réduire le coût du financement. La suppression de la révision par Moody's pourrait indiquer une stabilisation des perspectives de crédit. Cette modification affecte la transparence des notations de crédit, un élément crucial pour les parties prenantes évaluant le risque de crédit de la banque. Point de surveillance : Surveiller l'impact de ces changements de notation sur les conditions de financement et la perception du risque par les autres agences de notation.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Facteur de risque modifié Ce qui change : BNC modifie les notations de crédit en intégrant une révision à la hausse par S&amp;P Global Ratings et en supprimant une révision par Moody's. Pertinence métier : Ce changement met en évidence une amélioration de la perception du risque de crédit de la BNC par les agences de notation, ce qui peut influencer positivement la confiance des investisseurs et réduire les coûts de financement. La révision à la hausse par S&amp;P indique une amélioration de la qualité de crédit perçue, tandis que la suppression de la révision par Moody's pourrait signaler une stabilisation des notations. Cela affecte la transparence et la gestion des risques de crédit de la banque, en alignant ses notations sur les attentes du marché. Point de surveillance : Surveiller l'impact de ces changements de notation sur les conditions de financement et la perception du risque de crédit par d'autres parties prenantes.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1288,22 +1292,22 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Notations de crédit de la Banque</t>
+          <t>Sommaire des actifs grevés et non grevés (1) *</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1313,13 +1317,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Le 24 septembre 2024, Moody's a placé sous révision en vue d’une révision à la hausse toutes les notations et évaluations à long terme de la Banque, y compris son évaluation de crédit de base Baa1, les notations de dépôts à long terme Aa3 et les notations de risque de contrepartie, ainsi que son évaluation de risque de contrepartie de Aa3(cr).</t>
+          <t>Participations dans des entreprises associées et des coentreprises</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Facteur de risque modifié Ce qui change : BNC modifie les notations de crédit en intégrant une révision à la hausse par S&amp;P Global Ratings et en supprimant une révision par Moody's. Pertinence métier : Ce changement met en évidence une amélioration de la perception du risque de crédit de la BNC par S&amp;P, ce qui peut influencer positivement la confiance des investisseurs et réduire le coût du financement. La suppression de la révision par Moody's pourrait indiquer une stabilisation des perspectives de crédit. Cette modification affecte la transparence des notations de crédit, un élément crucial pour les parties prenantes évaluant le risque de crédit de la banque. Point de surveillance : Surveiller l'impact de ces changements de notation sur les conditions de financement et la perception du risque par les autres agences de notation.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport Ce qui change : BNC supprime les indicateurs relatifs aux participations dans des entreprises associées et des coentreprises du tableau Sommaire des actifs grevés et non grevés. Pertinence métier : Ce changement met en évidence une modification dans la structure de divulgation des actifs de la BNC, ce qui peut affecter la transparence et la comparabilité des informations financières fournies aux investisseurs et régulateurs. La suppression de ces indicateurs pourrait réduire la visibilité sur l'exposition de la banque à des entités associées, ce qui est crucial pour évaluer les risques de concentration et de dépendance. Cela pourrait également influencer la perception des risques de liquidité et de financement liés à ces actifs. Point de surveillance : Surveiller l'impact de cette suppression sur la transparence des rapports financiers et la capacité des parties prenantes à évaluer les risques associés aux actifs grevés et non grevés.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1339,17 +1343,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Sommaire des actifs grevés et non grevés (1) *</t>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1364,13 +1368,13 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Participations dans des entreprises associées et des coentreprises</t>
+          <t>Titrisation de créances sur cartes de crédit</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : BNC supprime les indicateurs relatifs aux participations dans des entreprises associées et des coentreprises du tableau Sommaire des actifs grevés et non grevés. Pertinence métier : Ce changement met en évidence une modification dans la manière dont la BNC présente ses actifs grevés et non grevés, ce qui peut affecter la transparence et la compréhension des risques associés à ces actifs. La suppression de ces indicateurs pourrait réduire la visibilité sur l'exposition de la banque à des entités associées, ce qui est crucial pour évaluer les risques de concentration et de dépendance. Cela peut également influencer la comparabilité avec d'autres institutions financières qui continuent de divulguer ces informations. Point de surveillance : Surveiller l'impact de cette suppression sur l'évaluation des risques de concentration et la transparence des rapports financiers de la BNC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur 'Titrisation de créances sur cartes de crédit' et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la présentation des échéances de financement, ce qui peut affecter la transparence et la compréhension des engagements financiers de la banque. La suppression de l'indicateur de titrisation de créances sur cartes de crédit pourrait indiquer un changement dans la stratégie de financement ou de gestion des risques de liquidité. Les modifications des notes, notamment l'inclusion des dettes sujettes à des règlements de conversion, soulignent une attention accrue aux exigences de recapitalisation interne, ce qui est crucial pour la résilience financière. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion de la liquidité et la conformité aux exigences réglementaires de recapitalisation interne.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1405,7 +1409,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1415,13 +1419,13 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Titrisation de créances sur cartes de crédit</t>
+          <t>Les certificats de dépôt libellés en euros sont inclus dans les billets de premier rang non garantis à moyen terme.</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur 'Titrisation de créances sur cartes de crédit' et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la présentation des échéances de financement, ce qui peut affecter la transparence et la compréhension des engagements financiers de la banque. La suppression de l'indicateur de titrisation de créances sur cartes de crédit pourrait indiquer un changement dans la stratégie de financement ou de gestion des risques de liquidité. Les modifications des notes, notamment l'inclusion des dettes sujettes à des règlements de conversion, soulignent une attention accrue aux exigences de recapitalisation interne, ce qui est crucial pour la résilience financière. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion de la liquidité et la conformité aux exigences réglementaires de recapitalisation interne.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1436,22 +1440,22 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
+          <t>(sans titre)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1461,18 +1465,18 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Les acceptations bancaires ne sont pas incluses dans ce tableau.</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisée conformément à l’approche utilisée par la Banque.</t>
+        </is>
+      </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Risque émergent : IA, cybersécurité, fraude, cryptoactifs ou modèles tiers Ce qui change : BNC modifie le tableau de gestion du capital pour inclure une note sur la variation du risque opérationnel liée à l'inclusion de CWB. Pertinence métier : Ce changement met en évidence l'impact de l'intégration de CWB sur le risque opérationnel de la BNC. L'ajout de cette note souligne l'importance de surveiller les risques émergents associés à l'intégration de nouvelles entités, notamment en matière de cybersécurité et de gestion des données. Cela renforce la transparence de la BNC quant à sa gestion des risques opérationnels et améliore la comparabilité avec ses pairs en termes de divulgation des risques. Point de surveillance : Surveiller l'évolution des risques opérationnels liés à l'intégration de CWB et l'impact potentiel sur la gestion des risques de la BNC.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1487,43 +1491,43 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Les certificats de dépôt libellés en euros sont inclus dans les billets de premier rang non garantis à moyen terme.</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Série 47</t>
+        </is>
+      </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Fonds propres réglementaires Ce qui change : BNC modifie le tableau des actions et autres instruments de capitaux propres en ajoutant les indicateurs Série 47 et Série 49, tout en supprimant l'indicateur Série 32. Pertinence métier : Ce changement met en évidence une réorganisation des instruments de capitaux propres de la BNC, ce qui peut refléter une stratégie de gestion du capital différente ou une réponse à des exigences réglementaires. L'ajout des Séries 47 et 49 pourrait indiquer l'émission de nouveaux instruments de capital, tandis que la suppression de la Série 32 pourrait signaler le rachat ou l'échéance d'un instrument existant. Cela affecte la transparence et la comparabilité des fonds propres réglementaires de la banque, influençant potentiellement sa capacité à répondre aux exigences de capital réglementaire. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la stratégie de gestion des fonds propres de la BNC.</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1543,22 +1547,22 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1569,12 +1573,12 @@
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisée conformément à l’approche utilisée par la Banque.</t>
+          <t>Série 49</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée Ce qui change : BNC modifie la méthode de calcul du risque opérationnel en incluant CWB dans ses évaluations. Pertinence métier : Ce changement met en évidence une modification dans la manière dont BNC évalue son risque opérationnel, en intégrant désormais les données de CWB. Cela peut avoir un impact significatif sur la gestion du risque opérationnel de la banque, car l'inclusion de nouvelles entités peut modifier les profils de risque et nécessiter des ajustements dans les stratégies de gestion des risques. Cette modification améliore la transparence et la précision des évaluations de risque, ce qui est crucial pour maintenir la résilience de la banque face aux risques opérationnels. Point de surveillance : Surveiller l'impact de l'inclusion de CWB sur les évaluations de risque opérationnel et les ajustements nécessaires dans les stratégies de gestion des risques.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Fonds propres réglementaires Ce qui change : BNC modifie le tableau des actions et autres instruments de capitaux propres en ajoutant les indicateurs Série 47 et Série 49, tout en supprimant l'indicateur Série 32. Pertinence métier : Ce changement met en évidence une réorganisation des instruments de capitaux propres de la BNC, ce qui peut refléter une stratégie de gestion du capital différente ou une réponse à des exigences réglementaires. L'ajout des Séries 47 et 49 pourrait indiquer l'émission de nouveaux instruments de capital, tandis que la suppression de la Série 32 pourrait signaler le rachat ou l'échéance d'un instrument existant. Cela affecte la transparence et la comparabilité des fonds propres réglementaires de la banque, influençant potentiellement sa capacité à répondre aux exigences de capital réglementaire. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la stratégie de gestion des fonds propres de la BNC.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1614,18 +1618,18 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Série 47</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Série 32</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : BNC modifie le tableau des actions et autres instruments de capitaux propres en ajoutant les indicateurs Série 47 et Série 49, tout en supprimant l'indicateur Série 32. Pertinence métier : Ce changement met en évidence une réorganisation des instruments de capitaux propres de la BNC, ce qui peut affecter la composition des fonds propres réglementaires. L'ajout des Séries 47 et 49 pourrait indiquer l'émission de nouveaux instruments de capital, tandis que la suppression de la Série 32 pourrait signaler le rachat ou l'échéance d'un instrument existant. Cela a un impact direct sur la structure du capital réglementaire et la capacité de la banque à répondre aux exigences de fonds propres. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la conformité aux exigences prudentielles.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Fonds propres réglementaires Ce qui change : BNC modifie le tableau des actions et autres instruments de capitaux propres en ajoutant les indicateurs Série 47 et Série 49, tout en supprimant l'indicateur Série 32. Pertinence métier : Ce changement met en évidence une réorganisation des instruments de capitaux propres de la BNC, ce qui peut refléter une stratégie de gestion du capital différente ou une réponse à des exigences réglementaires. L'ajout des Séries 47 et 49 pourrait indiquer l'émission de nouveaux instruments de capital, tandis que la suppression de la Série 32 pourrait signaler le rachat ou l'échéance d'un instrument existant. Cela affecte la transparence et la comparabilité des fonds propres réglementaires de la banque, influençant potentiellement sa capacité à répondre aux exigences de capital réglementaire. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la stratégie de gestion des fonds propres de la BNC.</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1645,22 +1649,22 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
+          <t>Capital réglementaire (1), ratio de levier (1) et TLAC (2)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1671,12 +1675,12 @@
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Série 49</t>
+          <t>Les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : BNC modifie le tableau des actions et autres instruments de capitaux propres en ajoutant les indicateurs Série 47 et Série 49, tout en supprimant l'indicateur Série 32. Pertinence métier : Ce changement met en évidence une réorganisation des instruments de capitaux propres de la BNC, ce qui peut affecter la composition des fonds propres réglementaires. L'ajout des Séries 47 et 49 pourrait indiquer l'émission de nouveaux instruments de capital, tandis que la suppression de la Série 32 pourrait signaler le rachat ou l'échéance d'un instrument existant. Cela a un impact direct sur la structure du capital réglementaire et la capacité de la banque à répondre aux exigences de fonds propres. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la conformité aux exigences prudentielles.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Ratio ou seuil prudentiel Ce qui change : BNC modifie le tableau du capital réglementaire en ajoutant des notes sur le rachat des BCRL - Série 1 effectué le 17 novembre 2025. Pertinence métier : Ce changement met en évidence l'impact du rachat des BCRL - Série 1 sur les données de capital réglementaire au 31 octobre 2025. Cela affecte directement les ratios de capital et de levier, influençant la capacité de la banque à respecter les exigences réglementaires en matière de fonds propres. La transparence accrue sur ces ajustements permet une meilleure évaluation de la solidité financière de la BNC par les régulateurs et les investisseurs. Point de surveillance : Surveiller l'impact de ce rachat sur les ratios de capital et de levier pour s'assurer que la BNC maintient sa conformité avec les exigences réglementaires.</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1696,38 +1700,38 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d’actions</t>
+          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Série 32</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
+        </is>
+      </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire Ce qui change : BNC modifie le tableau des actions et autres instruments de capitaux propres en ajoutant les indicateurs Série 47 et Série 49, tout en supprimant l'indicateur Série 32. Pertinence métier : Ce changement met en évidence une réorganisation des instruments de capitaux propres de la BNC, ce qui peut affecter la composition des fonds propres réglementaires. L'ajout des Séries 47 et 49 pourrait indiquer l'émission de nouveaux instruments de capital, tandis que la suppression de la Série 32 pourrait signaler le rachat ou l'échéance d'un instrument existant. Cela a un impact direct sur la structure du capital réglementaire et la capacité de la banque à répondre aux exigences de fonds propres. Point de surveillance : Surveiller l'impact de ces changements sur les ratios de capital réglementaire et la conformité aux exigences prudentielles.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Ratio ou seuil prudentiel, Capital réglementaire Ce qui change : BNC ajoute une note précisant que les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025. Pertinence métier : Ce changement met en évidence l'impact d'un événement postérieur à la date de clôture sur les ratios réglementaires de la BNC. En intégrant le rachat des BCRL - Série 1 dans ses calculs, la banque améliore la transparence et la précision de ses divulgations financières, ce qui est crucial pour les investisseurs et les régulateurs. Cela montre également une gestion proactive du capital, alignée avec les exigences réglementaires, et renforce la confiance dans la capacité de la banque à maintenir des niveaux de capital adéquats. Point de surveillance : Surveiller l'impact de ce rachat sur les ratios futurs et la stratégie de gestion du capital de la BNC.</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1747,22 +1751,22 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Capital réglementaire (1), ratio de levier (1) et TLAC (2)</t>
+          <t>Variation des fonds propres réglementaires (1)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1773,12 +1777,12 @@
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
+          <t>Émission d'actions ordinaires relatives à l'acquisition de CWB</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Capital réglementaire, Ratio ou seuil prudentiel Ce qui change : BNC modifie le tableau du capital réglementaire pour inclure des notes sur le rachat des BCRL - Série 1 effectué le 17 novembre 2025. Pertinence métier : Ce changement met en évidence l'impact du rachat des BCRL - Série 1 sur les ratios de capital réglementaire de la BNC. En intégrant ces données, la banque améliore la transparence de ses divulgations financières et permet une meilleure évaluation de sa position en capital par rapport aux exigences réglementaires. Cela pourrait également influencer la perception des investisseurs et des régulateurs sur la solidité financière de la banque. Point de surveillance : Surveiller l'impact de ce rachat sur les ratios de capital et de levier, ainsi que sur la conformité aux exigences TLAC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : BNC ajoute des indicateurs liés à l'émission d'actions ordinaires et aux options de remplacement dans le cadre de l'acquisition de CWB, et modifie les notes pour inclure le rachat des BCRL - Série 1. Pertinence métier : Ce changement met en évidence l'impact de l'acquisition de CWB sur les fonds propres réglementaires de la BNC. L'ajout de ces indicateurs reflète une augmentation potentielle du capital réglementaire, ce qui pourrait influencer les ratios de fonds propres et la capacité de la banque à absorber les chocs financiers. La modification des notes pour inclure le rachat des BCRL - Série 1 souligne également une gestion active des instruments de capital, ce qui est crucial pour maintenir la conformité avec les exigences réglementaires. Point de surveillance : Surveiller l'évolution des fonds propres réglementaires de la BNC suite à l'acquisition de CWB et l'impact sur les ratios de capital.</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1798,22 +1802,22 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
+          <t>Variation des fonds propres réglementaires (1)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1824,12 +1828,12 @@
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Les ratios au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
+          <t>Options de remplacement relatives à l'acquisition de CWB</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Ratio ou seuil prudentiel, Capital réglementaire Ce qui change : BNC modifie les notes du tableau des exigences réglementaires pour inclure l'impact du rachat des BCRL - Série 1 et met à jour la date de confirmation de la réserve pour stabilité intérieure par le BSIF. Pertinence métier : Ce changement met en évidence l'impact des événements récents sur les ratios réglementaires de la BNC, notamment le rachat des BCRL - Série 1. La mise à jour de la date de confirmation par le BSIF reflète une évolution dans la gestion des réserves de stabilité intérieure, ce qui peut influencer la perception de la solidité financière de la banque. Cela améliore la transparence et l'alignement avec les exigences réglementaires actuelles, tout en permettant une meilleure comparabilité avec les pairs. Point de surveillance : Surveiller l'impact du rachat sur les ratios de fonds propres et la conformité continue avec les exigences du BSIF.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : BNC ajoute des indicateurs liés à l'émission d'actions ordinaires et aux options de remplacement dans le cadre de l'acquisition de CWB, et modifie les notes pour inclure le rachat des BCRL - Série 1. Pertinence métier : Ce changement met en évidence l'impact de l'acquisition de CWB sur les fonds propres réglementaires de la BNC. L'ajout de ces indicateurs reflète une augmentation potentielle du capital réglementaire, ce qui pourrait influencer les ratios de fonds propres et la capacité de la banque à absorber les chocs financiers. La modification des notes pour inclure le rachat des BCRL - Série 1 souligne également une gestion active des instruments de capital, ce qui est crucial pour maintenir la conformité avec les exigences réglementaires. Point de surveillance : Surveiller l'évolution des fonds propres réglementaires de la BNC suite à l'acquisition de CWB et l'impact sur les ratios de capital.</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1864,23 +1868,27 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr"/>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Les données de 2023 n’ont pas été ajustées pour tenir compte des modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
+        </is>
+      </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Émission d'actions ordinaires relatives à l'acquisition de CWB</t>
+          <t>Les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : BNC ajoute des indicateurs liés à l'émission d'actions ordinaires et aux options de remplacement dans le cadre de l'acquisition de CWB, et modifie les notes pour inclure le rachat des BCRL - Série 1. Pertinence métier : Ce changement met en évidence l'impact de l'acquisition de CWB sur les fonds propres réglementaires de la BNC. L'ajout d'indicateurs spécifiques à cette acquisition souligne l'importance de cette transaction pour la structure du capital de la banque. Cela affecte la transparence et la comparabilité des fonds propres réglementaires, car il est crucial de comprendre comment les acquisitions influencent les ratios de capital et la capacité de la banque à respecter les exigences réglementaires. Point de surveillance : Surveiller l'évolution des fonds propres réglementaires de la BNC suite à l'acquisition de CWB et l'impact sur les ratios de capital.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : BNC ajoute des indicateurs liés à l'émission d'actions ordinaires et aux options de remplacement dans le cadre de l'acquisition de CWB, et modifie les notes pour inclure le rachat des BCRL - Série 1. Pertinence métier : Ce changement met en évidence l'impact de l'acquisition de CWB sur les fonds propres réglementaires de la BNC. L'ajout de ces indicateurs reflète une augmentation potentielle du capital réglementaire, ce qui pourrait influencer les ratios de fonds propres et la capacité de la banque à absorber les chocs financiers. La modification des notes pour inclure le rachat des BCRL - Série 1 souligne également une gestion active des instruments de capital, ce qui est crucial pour maintenir la conformité avec les exigences réglementaires. Point de surveillance : Surveiller l'évolution des fonds propres réglementaires de la BNC suite à l'acquisition de CWB et l'impact sur les ratios de capital.</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1893,110 +1901,110 @@
       <c r="M27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Options de remplacement relatives à l'acquisition de CWB</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : BNC ajoute des indicateurs liés à l'émission d'actions ordinaires et aux options de remplacement dans le cadre de l'acquisition de CWB, et modifie les notes pour inclure le rachat des BCRL - Série 1. Pertinence métier : Ce changement met en évidence l'impact de l'acquisition de CWB sur les fonds propres réglementaires de la BNC. L'ajout d'indicateurs spécifiques à cette acquisition souligne l'importance de cette transaction pour la structure du capital de la banque. Cela affecte la transparence et la comparabilité des fonds propres réglementaires, car il est crucial de comprendre comment les acquisitions influencent les ratios de capital et la capacité de la banque à respecter les exigences réglementaires. Point de surveillance : Surveiller l'évolution des fonds propres réglementaires de la BNC suite à l'acquisition de CWB et l'impact sur les ratios de capital.</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter aux notes 17 et 18 afférentes aux états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : BNC modifie le tableau de gestion des risques en supprimant l'indicateur 'Acceptations' et en renommant 'Prêts et acceptations, déduction faite des provisions' en 'Prêts, déduction faite des provisions'. Pertinence métier : Ce changement met en évidence une révision de la présentation des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent modifier la perception des risques de crédit et la manière dont la banque communique ses expositions. Cela pourrait également influencer la compréhension des risques par les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la communication des risques de crédit et la clarté des informations financières fournies par la BNC.</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Modification</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Les données de 2023 n’ont pas été ajustées pour tenir compte des modifications de méthodes comptables relatives à l’adoption de l’IFRS 17. Pour de plus amples renseignements, se reporter à la note 2 afférente aux présents états financiers consolidés.</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Les données au 31 octobre 2025 tiennent compte du rachat des BCRL - Série 1 effectué le 17 novembre 2025.</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Fonds propres réglementaires, Capital réglementaire Ce qui change : BNC ajoute des indicateurs liés à l'émission d'actions ordinaires et aux options de remplacement dans le cadre de l'acquisition de CWB, et modifie les notes pour inclure le rachat des BCRL - Série 1. Pertinence métier : Ce changement met en évidence l'impact de l'acquisition de CWB sur les fonds propres réglementaires de la BNC. L'ajout d'indicateurs spécifiques à cette acquisition souligne l'importance de cette transaction pour la structure du capital de la banque. Cela affecte la transparence et la comparabilité des fonds propres réglementaires, car il est crucial de comprendre comment les acquisitions influencent les ratios de capital et la capacité de la banque à respecter les exigences réglementaires. Point de surveillance : Surveiller l'évolution des fonds propres réglementaires de la BNC suite à l'acquisition de CWB et l'impact sur les ratios de capital.</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter aux notes 18 et 19 afférentes aux états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter à la note 23 afférente aux états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : BNC modifie le tableau de gestion des risques en supprimant l'indicateur 'Acceptations' et en renommant 'Prêts et acceptations, déduction faite des provisions' en 'Prêts, déduction faite des provisions'. Pertinence métier : Ce changement met en évidence une révision de la présentation des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent modifier la perception des risques de crédit et la manière dont la banque communique ses expositions. Cela pourrait également influencer la compréhension des risques par les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la communication des risques de crédit et la clarté des informations financières fournies par la BNC.</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2026,18 +2034,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Pour de plus amples renseignements, se reporter aux notes 17 et 18 afférentes aux états financiers consolidés.</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter à la note 25 afférente aux états financiers consolidés.</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Texte de risque modifié Ce qui change : BNC modifie le tableau de gestion des risques en supprimant l'indicateur 'Acceptations' et en renommant 'Prêts et acceptations, déduction faite des provisions' en 'Prêts, déduction faite des provisions'. Pertinence métier : Ce changement met en évidence une révision de la présentation des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières. La suppression de l'indicateur 'Acceptations' et le renommage des prêts peuvent modifier la perception des risques de crédit et la manière dont la banque communique ses expositions. Cela pourrait également influencer la compréhension des risques par les investisseurs et les régulateurs. Point de surveillance : Surveiller l'impact de ces modifications sur la communication des risques de crédit et la clarté des informations financières fournies par la BNC.</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2057,17 +2065,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2077,22 +2085,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Pour de plus amples renseignements, se reporter aux notes 18 et 19 afférentes aux états financiers consolidés.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Pour de plus amples renseignements, se reporter à la note 23 afférente aux états financiers consolidés.</t>
+          <t>Incluent les billets de dépôt au porteur.</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur 'Titrisation de créances sur cartes de crédit' et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la présentation des échéances de financement, ce qui peut affecter la transparence et la compréhension des engagements financiers de la banque. La suppression de l'indicateur de titrisation de créances sur cartes de crédit pourrait indiquer un changement dans la stratégie de financement ou de gestion des risques de liquidité. Les modifications des notes, notamment l'inclusion des dettes sujettes à des règlements de conversion, soulignent une attention accrue aux exigences de recapitalisation interne, ce qui est crucial pour la résilience financière. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion de la liquidité et la conformité aux exigences réglementaires de recapitalisation interne.</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2112,42 +2116,38 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Renommage</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Prêts et acceptations, déduction faite des provisions</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Prêts, déduction faite des provisions</t>
-        </is>
-      </c>
+          <t>Les acceptations bancaires ne sont pas incluses dans ce tableau.</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Méthode de calcul ou approche modifiée Ce qui change : BNC modifie les indicateurs en supprimant les participations dans des entreprises associées et des coentreprises, et en renommant les prêts et acceptations, déduction faite des provisions, en prêts, déduction faite des provisions. De plus, certaines notes ont été supprimées en raison de modifications de méthodes comptables liées à l'adoption de l'IFRS 17. Pertinence métier : Ce changement met en évidence une révision des méthodes comptables et des indicateurs de risque, ce qui peut affecter la transparence et la comparabilité des informations financières de la BNC. L'adoption de l'IFRS 17 pourrait avoir des implications sur la manière dont les actifs et passifs sont évalués, influençant ainsi la perception des risques financiers et la gestion des fonds propres. Cela pourrait également impacter la manière dont la BNC communique ses risques aux investisseurs et aux régulateurs. Point de surveillance : Surveiller l'impact de l'adoption de l'IFRS 17 sur les rapports financiers et la gestion des risques de la BNC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur 'Titrisation de créances sur cartes de crédit' et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la présentation des échéances de financement, ce qui peut affecter la transparence et la compréhension des engagements financiers de la banque. La suppression de l'indicateur de titrisation de créances sur cartes de crédit pourrait indiquer un changement dans la stratégie de financement ou de gestion des risques de liquidité. Les modifications des notes, notamment l'inclusion des dettes sujettes à des règlements de conversion, soulignent une attention accrue aux exigences de recapitalisation interne, ce qui est crucial pour la résilience financière. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion de la liquidité et la conformité aux exigences réglementaires de recapitalisation interne.</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2162,7 +2162,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -2170,35 +2170,27 @@
           <t>(sans titre)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
+      <c r="C33" s="4" t="inlineStr"/>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Pour de plus amples renseignements, se reporter à la note 25 afférente aux états financiers consolidés.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Texte de risque modifié, Structure du rapport Ce qui change : BNC modifie les indicateurs et les notes associées au tableau de gestion des risques, notamment en supprimant l'indicateur 'Acceptations' et en ajustant les références aux notes des états financiers consolidés. Pertinence métier : Ce changement met en évidence une révision de la présentation des risques liés aux activités de négociation, ce qui peut affecter la transparence et la compréhension des risques de marché par les parties prenantes. La suppression de l'indicateur 'Acceptations' et la modification des références aux notes financières peuvent influencer la manière dont les risques sont évalués et communiqués, impactant ainsi la comparabilité avec les rapports antérieurs et la gestion des risques par rapport aux pairs. Point de surveillance : Surveiller l'impact de ces modifications sur la clarté et la cohérence des divulgations de risques dans les futurs rapports financiers.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Gouvernance des risques Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs de risques tels que Crédit, Marché, Opérationnel et Autres risques. Pertinence métier : Ce changement met en évidence une amélioration de la transparence et de la gouvernance des risques de la BNC. L'ajout de ce tableau permet une meilleure visibilité sur la répartition et la gestion des différents types de risques auxquels la banque est exposée. Cela renforce la capacité des parties prenantes à évaluer la résilience de la banque face aux risques financiers et opérationnels, et améliore la comparabilité avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ce tableau sur la compréhension des risques par les investisseurs et les régulateurs, ainsi que sur la stratégie de gestion des risques de la BNC.</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2213,27 +2205,23 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Échéances contractuelles résiduelles du financement institutionnel *</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2242,14 +2230,10 @@
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Incluent les billets de dépôt au porteur.</t>
-        </is>
-      </c>
+      <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Liquidité Ce qui change : BNC modifie le tableau des échéances contractuelles résiduelles du financement institutionnel en supprimant l'indicateur de titrisation de créances sur cartes de crédit et en modifiant les notes associées. Pertinence métier : Ce changement met en évidence une révision de la manière dont BNC présente ses échéances de financement, ce qui peut affecter la transparence et la compréhension des risques de liquidité. La suppression de l'indicateur de titrisation de créances sur cartes de crédit et les modifications des notes peuvent influencer la perception des engagements financiers et la gestion des liquidités. Cela pourrait également avoir un impact sur la comparabilité avec les rapports précédents et avec d'autres institutions financières. Point de surveillance : Surveiller l'impact de ces modifications sur la gestion des liquidités et la transparence des divulgations financières de BNC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs liés aux risques de crédit, de marché et opérationnel, ainsi qu'un total. Pertinence métier : Ce changement met en évidence l'importance accrue accordée par la BNC à la transparence et à la gestion des risques financiers. L'ajout de ce tableau permet une meilleure visibilité sur la répartition et la gestion des risques de crédit, de marché et opérationnel, ce qui est crucial pour évaluer la résilience de la banque face aux chocs financiers. Cela améliore également la comparabilité avec les pairs en fournissant des informations structurées sur les risques et le capital réglementaire. Point de surveillance : Surveiller l'impact de ce tableau sur la compréhension des risques financiers et la conformité aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2269,42 +2253,30 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Le 18 juin 2024, le BSIF a confirmé que la réserve pour stabilité intérieure était maintenue à 3,5 %.</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Le 26 juin 2025, le BSIF a confirmé que la réserve pour stabilité intérieure était maintenue à 3,5%.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Ratio ou seuil prudentiel, Capital réglementaire Ce qui change : BNC modifie les notes du tableau des exigences réglementaires pour inclure l'impact du rachat des BCRL - Série 1 et met à jour la date de confirmation de la réserve pour stabilité intérieure par le BSIF. Pertinence métier : Ce changement met en évidence l'impact des événements récents sur les ratios réglementaires de la BNC, notamment le rachat des BCRL - Série 1. La mise à jour de la date de confirmation par le BSIF reflète une évolution dans la gestion des réserves de stabilité intérieure, ce qui peut influencer la perception de la solidité financière de la banque. Cela améliore la transparence et l'alignement avec les exigences réglementaires actuelles, tout en permettant une meilleure comparabilité avec les pairs. Point de surveillance : Surveiller l'impact du rachat sur les ratios de fonds propres et la conformité continue avec les exigences du BSIF.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs de crédit, de marché et opérationnels, ainsi que le total. Pertinence métier : Ce changement met en évidence une nouvelle approche de la BNC pour divulguer des informations sur les risques de crédit, de marché et opérationnels. L'ajout de ce tableau sans titre pourrait indiquer une volonté d'améliorer la transparence et la comparabilité des informations sur le capital réglementaire. Cela pourrait également refléter une réponse aux attentes réglementaires croissantes en matière de divulgation des risques, renforçant ainsi la résilience de la banque face aux chocs externes. Point de surveillance : Surveiller l'impact de ce nouveau tableau sur la transparence des divulgations de capital et la conformité aux exigences réglementaires.</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2347,7 +2319,7 @@
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Gouvernance des risques Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs de risque pour le crédit, le marché, l'opérationnel et d'autres risques. Pertinence métier : Ce changement met en évidence une amélioration de la transparence et de la gouvernance des risques de la BNC. L'ajout de ce tableau permet une meilleure compréhension des différents types de risques auxquels la banque est exposée, ce qui est crucial pour les actionnaires et les régulateurs. Cela renforce la capacité de la banque à communiquer efficacement sur sa gestion des risques et à se comparer à ses pairs en termes de divulgation de risques. Point de surveillance : Surveiller l'impact de ce tableau sur la perception des risques par les investisseurs et les régulateurs, ainsi que sur la stratégie de gestion des risques de la BNC.</t>
+          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs liés aux risques de crédit, de marché et opérationnel, ainsi que le total. Pertinence métier : Ce changement met en évidence l'engagement de la BNC à renforcer la transparence de ses divulgations en matière de gestion du capital. L'ajout de ce tableau permet une meilleure compréhension des composantes de risque qui influencent le capital réglementaire de la banque. Cela améliore la comparabilité avec les pairs et la capacité des parties prenantes à évaluer la résilience de la banque face aux risques financiers. Point de surveillance : Surveiller l'impact de ce tableau sur la perception des risques de capital par les investisseurs et les régulateurs.</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2359,137 +2331,8 @@
       <c r="L36" s="4" t="inlineStr"/>
       <c r="M36" s="4" t="inlineStr"/>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Tableau</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs liés aux risques de crédit, de marché et opérationnel, ainsi que le total. Pertinence métier : Ce changement met en évidence une amélioration de la transparence dans la divulgation des risques financiers et de leur impact sur le capital réglementaire de la banque. En ajoutant ce tableau, BNC fournit une vue plus détaillée et structurée des composantes de risque qui influencent ses exigences en capital, ce qui est crucial pour les investisseurs et les régulateurs. Cela permet également une meilleure comparabilité avec les pairs et une évaluation plus précise de la résilience de la banque face aux chocs financiers. Point de surveillance : Surveiller l'impact de cette nouvelle divulgation sur la perception des risques par les parties prenantes et son alignement avec les exigences réglementaires.</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="4" t="inlineStr"/>
-      <c r="M37" s="4" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Tableau</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs liés aux risques de crédit, de marché et opérationnel. Pertinence métier : Ce changement met en évidence une amélioration de la transparence dans la divulgation des risques financiers de la BNC. En ajoutant un tableau spécifique aux indicateurs de risque, la banque fournit une vue plus détaillée et structurée de son exposition aux risques de crédit, de marché et opérationnel. Cela renforce la capacité des parties prenantes à évaluer la résilience de la banque face aux chocs financiers et à comparer sa gestion des risques avec celle de ses pairs. Point de surveillance : Surveiller l'impact de cette nouvelle divulgation sur la compréhension des risques financiers par les investisseurs et les régulateurs.</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="4" t="inlineStr"/>
-      <c r="M38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>(sans titre)</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Tableau</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui Sujet détecté : Structure du rapport, Capital réglementaire Ce qui change : BNC ajoute un nouveau tableau dans la section gestion du capital, présentant des indicateurs liés aux risques de crédit, de marché et opérationnel, ainsi que le total. Pertinence métier : Ce changement met en évidence une nouvelle approche de la BNC pour la divulgation de ses risques financiers, en intégrant un tableau qui synthétise les indicateurs clés de risque. Cela améliore la transparence et la comparabilité des informations sur le capital réglementaire, ce qui est crucial pour les investisseurs et les régulateurs. En fournissant une vue consolidée des risques, la BNC renforce sa capacité à démontrer sa résilience face aux chocs financiers potentiels. Point de surveillance : Surveiller l'impact de ce tableau sur la compréhension des risques financiers et la conformité aux exigences réglementaires.</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr"/>
-      <c r="M39" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M39"/>
+  <autoFilter ref="A1:M36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>